--- a/Weekly Progress Plan for BUS 311 Corporate Finance- Fall 2026.xlsx
+++ b/Weekly Progress Plan for BUS 311 Corporate Finance- Fall 2026.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bethanyevittsair2/Documents/GitHub/BUS311-Corporate_Finance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E1E9EEC-D7F5-964E-BAC6-535C49B562A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A57F7BE-1226-EF4C-9651-C4C864E86383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="880" windowWidth="34920" windowHeight="18980" tabRatio="711" activeTab="4" xr2:uid="{93B6D4D0-7CB4-48F5-B203-2BFD63CD9799}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="15120" tabRatio="711" activeTab="1" xr2:uid="{93B6D4D0-7CB4-48F5-B203-2BFD63CD9799}"/>
   </bookViews>
   <sheets>
     <sheet name="__FDSCACHE__" sheetId="10" state="veryHidden" r:id="rId1"/>
-    <sheet name=" Plan- SP26" sheetId="3" r:id="rId2"/>
+    <sheet name=" Plan- FA26" sheetId="3" r:id="rId2"/>
     <sheet name="SP26 Order" sheetId="17" r:id="rId3"/>
     <sheet name="Company Project Tracker " sheetId="15" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="16" r:id="rId5"/>
@@ -34,6 +34,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Score Sheet'!$A$1:$D$34</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4094,56 +4095,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4444,10 +4445,10 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>170</v>
-    <v>122.3</v>
-    <v>0.62029999999999996</v>
-    <v>-2.0750000000000002</v>
-    <v>-1.3327E-2</v>
+    <v>123.78</v>
+    <v>0.62219999999999998</v>
+    <v>0.36</v>
+    <v>2.3219999999999998E-3</v>
     <v>USD</v>
     <v>The TJX Companies, Inc. is an off-price apparel and home fashions retailer in the United States (U.S.) and worldwide. The Company's segments include Marmaxx and HomeGoods, both in the U.S., TJX Canada and TJX International, including Europe and Australia. The TJ Maxx and Marshalls chains sell family apparel, including footwear and accessories, home fashions, including home basics, decorative accessories, and giftware and other merchandise. The HomeGoods segment operates HomeGoods and Homesense chains. HomeGoods offers an eclectic assortment of home fashions, including furniture, rugs, lighting, soft home, decorative accessories, tabletop, and cookware, as well as expanded pet and gourmet food departments. The TJX Canada segment operates the Winners, HomeSense and Marshalls chains in Canada, offering a range of home decor, furniture, and seasonal home merchandise. The TJX International segment operates the TK Maxx and Homesense chains in Europe and the TK Maxx chain in Australia.</v>
     <v>377000</v>
@@ -4455,24 +4456,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>770 Cochituate Rd, FRAMINGHAM, MA, 01701 US</v>
-    <v>155.3725</v>
+    <v>158</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46224.664039953124</v>
+    <v>46225.99725224531</v>
     <v>0</v>
-    <v>152.77000000000001</v>
-    <v>169710152000</v>
+    <v>154.04</v>
+    <v>171682048640</v>
     <v>THE TJX COMPANIES, INC.</v>
     <v>THE TJX COMPANIES, INC.</v>
-    <v>154.965</v>
-    <v>29.842300000000002</v>
-    <v>155.69999999999999</v>
-    <v>153.625</v>
+    <v>155.79</v>
+    <v>30.1891</v>
+    <v>155.05000000000001</v>
+    <v>155.41</v>
     <v>1104704000</v>
     <v>TJX</v>
     <v>THE TJX COMPANIES, INC. (XNYS:TJX)</v>
-    <v>1514664</v>
-    <v>5906808</v>
+    <v>1240</v>
+    <v>5901287</v>
     <v>1962</v>
   </rv>
   <rv s="2">
@@ -4496,9 +4497,9 @@
     <v>Powered by Refinitiv</v>
     <v>20.28</v>
     <v>8</v>
-    <v>0.93089999999999995</v>
-    <v>-0.24</v>
-    <v>-1.2685E-2</v>
+    <v>0.93530000000000002</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>Callaway Golf Company, formerly Topgolf Callaway Brands Corp., is a golf equipment, gear and apparel company. The Company designs, manufactures, and sells high-performance golf clubs, golf balls, apparel, bags, and other accessories. Its products are distributed through a mix of on-course, specialty retail, wholesale, direct-to-consumer and international channels. It operates through two segments: Golf Equipment, Apparel, Gear and Other. Golf Equipment segment consists of golf club and golf ball products, including Callaway Golf-branded woods, hybrids, irons, wedges, Odyssey putters, packaged sets, Callaway Golf-branded golf balls and sales of pre-owned golf clubs. Apparel, Gear and Other segments consist of TravisMathew golf and lifestyle apparel and accessories business. Its golf club products include woods, drivers, fairway woods, hybrids and irons and wedges. It offers a two-piece golf ball consisting of a core and cover or a multilayer golf ball with two or more components.</v>
     <v>28000</v>
@@ -4506,24 +4507,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>2180 Rutherford Rd, CARLSBAD, CA, 92008-8815 US</v>
-    <v>19.34</v>
+    <v>18.64</v>
     <v>Leisure Products</v>
     <v>Stock</v>
-    <v>46224.664041955468</v>
+    <v>46225.982033240623</v>
     <v>3</v>
-    <v>18.495000000000001</v>
-    <v>3357871968</v>
+    <v>18.28</v>
+    <v>3300349536</v>
     <v>CALLAWAY GOLF COMPANY</v>
     <v>CALLAWAY GOLF COMPANY</v>
-    <v>18.984999999999999</v>
-    <v>32.852600000000002</v>
-    <v>18.920000000000002</v>
-    <v>18.68</v>
+    <v>18.329999999999998</v>
+    <v>32.2898</v>
+    <v>18.36</v>
+    <v>18.36</v>
     <v>179757600</v>
     <v>CALY</v>
     <v>CALLAWAY GOLF COMPANY (XNYS:CALY)</v>
-    <v>716235</v>
-    <v>2249513</v>
+    <v>6</v>
+    <v>2264174</v>
     <v>1999</v>
   </rv>
   <rv s="2">
@@ -4539,7 +4540,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>bvsk7w</v>
     <v>268435456</v>
@@ -4547,9 +4548,9 @@
     <v>Powered by Refinitiv</v>
     <v>207.52</v>
     <v>106.37</v>
-    <v>1.5670999999999999</v>
-    <v>-0.67</v>
-    <v>-4.9680000000000002E-3</v>
+    <v>1.5831999999999999</v>
+    <v>-8.09</v>
+    <v>-6.0983000000000002E-2</v>
     <v>USD</v>
     <v>Palantir Technologies Inc. is engaged in building software to assist in counterterrorism investigations and operations. The Company has built four principal software platforms, including Palantir Gotham (Gotham), Palantir Foundry (Foundry), Palantir Apollo (Apollo), and Palantir Artificial Intelligence Platform (AIP). Apollo is a cloud-agnostic, single control layer that coordinates ongoing delivery of new features, security updates, and platform configurations, helping to ensure the continuous operation of critical systems. Gotham enables users to identify patterns hidden deep within datasets, ranging from signals intelligence sources to reports from confidential informants. Foundry transforms the ways organizations operate by creating a central operating system for their data. AIP enables responsible artificial intelligence (AI)-advantage across the enterprise by using primary, core components built to effectively activate large language models and other AI within any organization.</v>
     <v>4395</v>
@@ -4557,24 +4558,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1200 17Th Street, Floor 15, DENVER, CO, 80202 US</v>
-    <v>134.68</v>
+    <v>132.345</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46224.664080566406</v>
+    <v>46225.999992731253</v>
     <v>6</v>
-    <v>131.22499999999999</v>
-    <v>321671324160</v>
+    <v>123.45</v>
+    <v>298633155840</v>
     <v>PALANTIR TECHNOLOGIES INC.</v>
     <v>PALANTIR TECHNOLOGIES INC.</v>
-    <v>133.80000000000001</v>
-    <v>151.17169999999999</v>
-    <v>134.85</v>
-    <v>134.18</v>
+    <v>132.22</v>
+    <v>140.3511</v>
+    <v>132.66</v>
+    <v>124.57</v>
     <v>2397312000</v>
     <v>PLTR</v>
     <v>PALANTIR TECHNOLOGIES INC. (XNAS:PLTR)</v>
-    <v>10381901</v>
-    <v>42927425</v>
+    <v>406195</v>
+    <v>42434953</v>
     <v>2003</v>
   </rv>
   <rv s="2">
@@ -4590,7 +4591,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a25xjc</v>
     <v>268435456</v>
@@ -4598,9 +4599,9 @@
     <v>Powered by Refinitiv</v>
     <v>248.13</v>
     <v>194.11</v>
-    <v>0.43330000000000002</v>
-    <v>-5.21</v>
-    <v>-2.1794999999999998E-2</v>
+    <v>0.43880000000000002</v>
+    <v>3.2</v>
+    <v>1.3723000000000001E-2</v>
     <v>USD</v>
     <v>Waste Management, Inc. is a provider of environmental solutions. The Company provides collection, recycling, and disposal services to millions of residential, commercial, industrial, and municipal customers throughout the United States and Canada. Its segments include East Tier, West Tier, Recycling Processing and Sales, WM Renewable Energy, and WM Healthcare Solutions. East Tier primarily consists of geographic areas located in the Eastern U.S., the Great Lakes region and all of Canada. The West Tier primarily includes geographic areas located in the Western U.S., including the upper Midwest region and British Columbia, Canada. Recycling Processing and Sales includes the processing and sales of materials collected from residential, commercial, and industrial customers. WM Renewable Energy develops, operates, and promotes projects for the beneficial use of landfill gas. WM Healthcare Solutions includes Regulated Waste and Compliance Services and Secure Information Destruction services.</v>
     <v>60500</v>
@@ -4608,24 +4609,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>800 Capitol Street, Suite 3000, HOUSTON, TX, 77002 US</v>
-    <v>235.93</v>
+    <v>236.76</v>
     <v>Professional &amp; Commercial Services</v>
     <v>Stock</v>
-    <v>46224.663978251563</v>
+    <v>46225.998087557811</v>
     <v>9</v>
-    <v>232.86</v>
-    <v>93904461688</v>
+    <v>233.41</v>
+    <v>94924463966</v>
     <v>WASTE MANAGEMENT, INC.</v>
     <v>WASTE MANAGEMENT, INC.</v>
-    <v>235.06</v>
-    <v>33.8506</v>
-    <v>239.05</v>
-    <v>233.84</v>
+    <v>235.17</v>
+    <v>34.218299999999999</v>
+    <v>233.18</v>
+    <v>236.38</v>
     <v>401575700</v>
     <v>WM</v>
     <v>WASTE MANAGEMENT, INC. (XNYS:WM)</v>
-    <v>739328</v>
-    <v>2224904</v>
+    <v>386</v>
+    <v>2182910</v>
     <v>1995</v>
   </rv>
   <rv s="2">
@@ -4641,7 +4642,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a24kar</v>
     <v>268435456</v>
@@ -4649,9 +4650,9 @@
     <v>Powered by Refinitiv</v>
     <v>498.83</v>
     <v>297.82</v>
-    <v>1.8216000000000001</v>
-    <v>12.21</v>
-    <v>3.3037999999999998E-2</v>
+    <v>1.8150999999999999</v>
+    <v>-4.92</v>
+    <v>-1.2984000000000001E-2</v>
     <v>USD</v>
     <v>Tesla, Inc. designs, develops, manufactures, sells and leases high-performance fully electric vehicles and energy generation and storage systems, and offers services related to its products. Its segments include automotive, and energy generation and storage. The automotive segment includes the design, development, manufacturing, sales and leasing of high-performance fully electric vehicles, and sales of automotive regulatory credits. It also includes sales of used vehicles, non-warranty maintenance services and collisions, part sales, paid supercharging, insurance services revenue and retail merchandise sales. The energy generation and storage segment include the design, manufacture, installation, sales and leasing of solar energy generation and energy storage products and related services and sales of solar energy systems incentives. Its consumer vehicles include the Model 3, Y, S, X and Cybertruck. Its lithium-ion battery energy storage products include Powerwall and Megapack.</v>
     <v>134785</v>
@@ -4659,24 +4660,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1 Tesla Road, AUSTIN, TX, 78725 US</v>
-    <v>384.07</v>
+    <v>380.17</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46224.664094803127</v>
+    <v>46225.999998402345</v>
     <v>12</v>
-    <v>369.99</v>
-    <v>1433860308720</v>
+    <v>372.9</v>
+    <v>1404678333240</v>
     <v>TESLA, INC.</v>
     <v>TESLA, INC.</v>
-    <v>370.66</v>
-    <v>348.9443</v>
-    <v>369.57</v>
-    <v>381.78</v>
+    <v>375.53</v>
+    <v>347.41539999999998</v>
+    <v>378.93</v>
+    <v>374.01</v>
     <v>3755724000</v>
     <v>TSLA</v>
     <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>17272090</v>
-    <v>42632578</v>
+    <v>2649880</v>
+    <v>41395900</v>
     <v>2024</v>
   </rv>
   <rv s="2">
@@ -4692,7 +4693,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a22k9c</v>
     <v>268435456</v>
@@ -4700,9 +4701,9 @@
     <v>Powered by Refinitiv</v>
     <v>109.23</v>
     <v>77.989999999999995</v>
-    <v>0.95589999999999997</v>
-    <v>0.03</v>
-    <v>2.8620000000000002E-4</v>
+    <v>0.95960000000000001</v>
+    <v>-0.47</v>
+    <v>-4.5000000000000005E-3</v>
     <v>USD</v>
     <v>Starbucks Corporations is a roaster, marketer, and retailer of specialty coffee globally. Its North America segment includes the United States and Canada. Its International segment includes China, Japan, Asia Pacific, Europe, Middle East and Africa, Latin America, and the Caribbean. Its North America and International segments include both Company-operated and licensed stores. The Channel Development segment includes roasted whole bean and ground coffees, Starbucks-branded single-serve products, a variety of ready-to-drink beverages, such as Frappuccino and Starbucks Doubleshot, foodservice products, and other branded products sold outside the Company-operated and licensed stores. A large portion of its Channel Development business operates under a licensed model of the Global Coffee Alliance with Nestle, while its global ready-to-drink businesses operate under collaborative relationships with PepsiCo, Inc., Tingyi-Ashi Beverages Holding Co., Ltd., Arla Foods amba, Nestle, and others.</v>
     <v>381000</v>
@@ -4710,24 +4711,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2401 Utah Ave S, Ms: S-La1, SEATTLE, WA, 98134 US</v>
-    <v>105.49</v>
+    <v>105.72</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46224.664091191407</v>
+    <v>46225.999662557813</v>
     <v>15</v>
-    <v>103.92</v>
-    <v>119486148000</v>
+    <v>102.91</v>
+    <v>118506006000</v>
     <v>STARBUCKS CORPORATION</v>
     <v>STARBUCKS CORPORATION</v>
-    <v>105.06</v>
-    <v>80.012200000000007</v>
-    <v>104.81</v>
-    <v>104.84</v>
+    <v>104.03</v>
+    <v>79.3553</v>
+    <v>104.45</v>
+    <v>103.98</v>
     <v>1139700000</v>
     <v>SBUX</v>
     <v>STARBUCKS CORPORATION (XNAS:SBUX)</v>
-    <v>2340621</v>
-    <v>7064338</v>
+    <v>4454</v>
+    <v>7091890</v>
     <v>1985</v>
   </rv>
   <rv s="2">
@@ -4743,17 +4744,17 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a25552</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>214.5</v>
-    <v>143.56</v>
-    <v>0.29609999999999997</v>
-    <v>1.87</v>
-    <v>9.6170000000000005E-3</v>
+    <v>149.11000000000001</v>
+    <v>0.29699999999999999</v>
+    <v>1.21</v>
+    <v>6.2480000000000001E-3</v>
     <v>USD</v>
     <v>RTX Corporation is an aerospace and defense company, which provides advanced systems and services for commercial, military, and government customers worldwide. The Company operates through three segments: Collins Aerospace, Pratt &amp; Whitney, and Raytheon. Collins Aerospace segment provides technologically advanced aerospace and defense products and aftermarket service solutions for civil and military aircraft manufacturers, commercial airlines, and regional, business and general aviation, as well as for defense and commercial space operations. The Pratt &amp; Whitney segment supplies aircraft engines for commercial, military, business jet, and general aviation customers. The Raytheon segment provides defensive and offensive threat detection, tracking and mitigation capabilities for the United States and foreign government and commercial customers. The Raytheon designs, develops, and provides advanced capabilities in integrated air and missile defense, smart weapons, missiles and others.</v>
     <v>180000</v>
@@ -4761,24 +4762,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1000 Wilson Blvd, ARLINGTON, VA, 22209 US</v>
-    <v>197.14009999999999</v>
+    <v>197.34989999999999</v>
     <v>Aerospace &amp; Defense</v>
     <v>Stock</v>
-    <v>46224.664085231248</v>
+    <v>46225.999734548437</v>
     <v>18</v>
-    <v>190.02</v>
-    <v>264367339730</v>
+    <v>193.7775</v>
+    <v>262441583040</v>
     <v>RTX CORPORATION</v>
     <v>RTX CORPORATION</v>
-    <v>193.99</v>
-    <v>36.786299999999997</v>
-    <v>194.44</v>
-    <v>196.31</v>
+    <v>195.9</v>
+    <v>36.5184</v>
+    <v>193.67</v>
+    <v>194.88</v>
     <v>1346683000</v>
     <v>RTX</v>
     <v>RTX CORPORATION (XNYS:RTX)</v>
-    <v>935080</v>
-    <v>4788997</v>
+    <v>149705</v>
+    <v>4796159</v>
     <v>1934</v>
   </rv>
   <rv s="2">
@@ -4794,42 +4795,42 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1u3rw</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>408.61</v>
-    <v>186.15</v>
-    <v>1.242</v>
-    <v>-2.16</v>
-    <v>-6.1370000000000001E-3</v>
+    <v>187.82</v>
+    <v>1.2442</v>
+    <v>-5.0599999999999996</v>
+    <v>-1.4576E-2</v>
     <v>USD</v>
     <v>Alphabet Inc. is a holding company. The Company's segments include Google Services, Google Cloud, and Other Bets. The Google Services segment includes products and services such as ads, Android, Chrome, devices, Google Maps, Google Play, Search, and YouTube. The Google Cloud segment includes infrastructure and platform services, collaboration tools, and other services for enterprise customers. Its Other Bets segment is engaged in the sale of healthcare-related services and Internet services. Its Google Cloud provides enterprise-ready cloud services, including Google Cloud Platform and Google Workspace. Google Cloud Platform provides access to solutions such as artificial intelligence (AI) offerings, including its AI infrastructure, Vertex AI platform, and Gemini for Google Cloud; cybersecurity, and data and analytics. Google Workspace includes cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet.</v>
-    <v>194668</v>
+    <v>198933</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1600 Amphitheatre Parkway, MOUNTAIN VIEW, CA, 94043 US</v>
-    <v>351.14</v>
+    <v>349.94</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46224.664078390626</v>
+    <v>46225.999991075783</v>
     <v>21</v>
-    <v>347.59</v>
-    <v>4259026324800</v>
+    <v>341.73</v>
+    <v>4164795230399</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
-    <v>350.79</v>
-    <v>26.663900000000002</v>
-    <v>351.99</v>
-    <v>349.83</v>
+    <v>348.15499999999997</v>
+    <v>17.1751</v>
+    <v>347.15</v>
+    <v>342.09</v>
     <v>12174560000</v>
     <v>GOOGL</v>
     <v>ALPHABET INC. (XNAS:GOOGL)</v>
-    <v>8628001</v>
-    <v>33354292</v>
+    <v>2303426</v>
+    <v>33299845</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -4845,7 +4846,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>bqrtfr</v>
     <v>268435456</v>
@@ -4853,9 +4854,9 @@
     <v>Powered by Refinitiv</v>
     <v>48.78</v>
     <v>20.46</v>
-    <v>1.6528</v>
-    <v>-0.16500000000000001</v>
-    <v>-6.7850000000000002E-3</v>
+    <v>1.6579999999999999</v>
+    <v>-1.02</v>
+    <v>-4.2766999999999999E-2</v>
     <v>USD</v>
     <v>DraftKings Inc. is a digital sports entertainment and gaming company. It provides users with online and retail sports betting (together, Sportsbook), online casino (iGaming) and daily fantasy sports product offerings, as well as digital lottery courier, media, and other product offerings. Sportsbook is live with mobile and/or retail sports betting operations pursuant to regulations in 28 states, Washington, D.C., and in Ontario, Canada. It operates iGaming pursuant to regulations in five states and in Ontario, Canada under its DraftKings brand and pursuant to regulations in four states under its Golden Nugget Online Gaming brand. It owns Jackpocket, a digital lottery courier app in the United States. It is both an official daily fantasy and sports betting partner of the NFL, NHL, PGA TOUR, WNBA and UFC, as well as an official daily fantasy partner of NASCAR, an official sports betting partner of the NBA. It also owns and operates DraftKings Network, a multi-platform content ecosystem.</v>
     <v>5500</v>
@@ -4863,24 +4864,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>222 Berkeley Street, 5th Floor, BOSTON, MA, 02116 US</v>
-    <v>24.33</v>
+    <v>23.81</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46224.66407528906</v>
+    <v>46225.999761503903</v>
     <v>24</v>
-    <v>23.84</v>
-    <v>11983991164</v>
+    <v>22.31</v>
+    <v>11326620504</v>
     <v>DRAFTKINGS INC.</v>
     <v>DRAFTKINGS INC.</v>
-    <v>24.1</v>
-    <v>281.8553</v>
-    <v>24.32</v>
-    <v>24.155000000000001</v>
+    <v>23.81</v>
+    <v>266.3322</v>
+    <v>23.85</v>
+    <v>22.83</v>
     <v>496128800</v>
     <v>DKNG</v>
     <v>DRAFTKINGS INC. (XNAS:DKNG)</v>
-    <v>4342901</v>
-    <v>11369313</v>
+    <v>14785</v>
+    <v>11190419</v>
     <v>2021</v>
   </rv>
   <rv s="2">
@@ -4890,11 +4891,11 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1x8nm&amp;q=XNYS%3aLYV&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="1">
-    <v>0</v>
+  <rv s="3">
+    <v>6</v>
     <v>LIVE NATION ENTERTAINMENT, INC. (XNYS:LYV)</v>
     <v>2</v>
-    <v>3</v>
+    <v>7</v>
     <v>Finance</v>
     <v>4</v>
     <v>en-US</v>
@@ -4904,9 +4905,9 @@
     <v>Powered by Refinitiv</v>
     <v>188</v>
     <v>125.34</v>
-    <v>1.1221000000000001</v>
-    <v>-3.605</v>
-    <v>-1.9932999999999999E-2</v>
+    <v>1.1234999999999999</v>
+    <v>0.09</v>
+    <v>5.061E-4</v>
     <v>USD</v>
     <v>Live Nation Entertainment, Inc. is a live entertainment company. The Company is a producer of live music concerts. Its segments include Concerts, Ticketing and Sponsorship &amp; Advertising. The Concerts segment principally involves the global promotion of live music events in its owned or operated venues and in rented third-party venues, the operation and management of music venues, the production of music festivals across the world, the creation of associated content and the provision of management and other services to artists. The Ticketing segment is an agency business that sells tickets for events on behalf of its clients. The Sponsorship &amp; Advertising segment employs a sales force that creates and maintains relationships with sponsors through a combination of strategic, international, national, and local opportunities that allow businesses to reach customers through its concert, festival, venue and ticketing assets, including advertising on its Websites.</v>
     <v>17700</v>
@@ -4914,24 +4915,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>9348 Civic Center Dr, BEVERLY HILLS, CA, 90210 US</v>
-    <v>179.85</v>
+    <v>180.17500000000001</v>
     <v>Media &amp; Publishing</v>
     <v>Stock</v>
-    <v>46224.664044050784</v>
+    <v>46225.992958784373</v>
     <v>27</v>
-    <v>176.24</v>
-    <v>41249507364</v>
+    <v>176.59</v>
+    <v>41404261376</v>
     <v>LIVE NATION ENTERTAINMENT, INC.</v>
     <v>LIVE NATION ENTERTAINMENT, INC.</v>
-    <v>179.18</v>
-    <v>0</v>
-    <v>180.86</v>
-    <v>177.255</v>
+    <v>177.76</v>
+    <v>177.83</v>
+    <v>177.92</v>
     <v>232712800</v>
     <v>LYV</v>
     <v>LIVE NATION ENTERTAINMENT, INC. (XNYS:LYV)</v>
-    <v>492507</v>
-    <v>2486738</v>
+    <v>455</v>
+    <v>2501722</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -4945,12 +4945,12 @@
     <v>http://en.wikipedia.org/wiki/McDonald's</v>
     <v>Wikipedia</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>30</v>
     <v>31</v>
   </rv>
-  <rv s="4">
-    <v>9</v>
+  <rv s="5">
+    <v>12</v>
     <v>https://www.bing.com/th?id=AMMS_7d8255243964a8970376f8dd41121106&amp;qlt=95</v>
     <v>32</v>
     <v>0</v>
@@ -4961,23 +4961,23 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1xdec&amp;q=XNYS%3aMCD&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
+    <v>8</v>
+    <v>MCDONALD'S CORPORATION (XNYS:MCD)</v>
+    <v>10</v>
+    <v>11</v>
+    <v>Finance</v>
     <v>5</v>
-    <v>MCDONALD'S CORPORATION (XNYS:MCD)</v>
-    <v>7</v>
-    <v>8</v>
-    <v>Finance</v>
-    <v>4</v>
     <v>en-US</v>
     <v>a1xdec</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>341.75</v>
-    <v>264.08999999999997</v>
-    <v>0.4148</v>
-    <v>-2.98</v>
-    <v>-1.1134E-2</v>
+    <v>261.85000000000002</v>
+    <v>0.41599999999999998</v>
+    <v>-0.34</v>
+    <v>-1.2880000000000001E-3</v>
     <v>USD</v>
     <v>McDonald's Corporation is a global foodservice retailer. Its segment includes U.S., International Operated Markets, and International Developmental Licensed Markets &amp; Corporate. The U.S. segment is its largest market and is 95% franchised. The International Operated Markets segment comprises markets or countries in which it operates and franchises restaurants, including Australia, Canada, France, Germany, Italy, Poland, Spain, and the United Kingdom. This segment is 89% franchised. The International Developmental Licensed Markets &amp; Corporate segment comprises development licensee and affiliate markets, including equity method investments in China and Japan. This segment is 99% franchised. Its menu features hamburgers and cheeseburgers, the Big Mac, the Quarter Pounder with Cheese, the Filet-O-Fish, and several chicken sandwiches, such as the McChicken and McCrispy as well as Chicken McNuggets, Fries, shakes, sundaes, cookies, soft drinks, coffee, and other beverages.</v>
     <v>150000</v>
@@ -4985,25 +4985,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>110 N Carpenter St, CHICAGO, IL, 60607-2104 US</v>
-    <v>266.86770000000001</v>
+    <v>265.97000000000003</v>
     <v>33</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46224.66408884219</v>
+    <v>46225.999661017966</v>
     <v>34</v>
-    <v>264.20999999999998</v>
-    <v>188042491494</v>
+    <v>261.85000000000002</v>
+    <v>187268040063</v>
     <v>MCDONALD'S CORPORATION</v>
     <v>MCDONALD'S CORPORATION</v>
-    <v>266.7</v>
-    <v>21.8156</v>
-    <v>267.64</v>
-    <v>264.66000000000003</v>
+    <v>265.7</v>
+    <v>21.7257</v>
+    <v>263.91000000000003</v>
+    <v>263.57</v>
     <v>710505900</v>
     <v>MCD</v>
     <v>MCDONALD'S CORPORATION (XNYS:MCD)</v>
-    <v>1112456</v>
-    <v>4765367</v>
+    <v>13934</v>
+    <v>4745794</v>
     <v>1964</v>
   </rv>
   <rv s="2">
@@ -5013,12 +5013,12 @@
     <v>https://en.wikipedia.org/wiki/Microsoft</v>
     <v>Wikipedia</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>30</v>
     <v>37</v>
   </rv>
-  <rv s="4">
-    <v>9</v>
+  <rv s="5">
+    <v>12</v>
     <v>https://www.bing.com/th?id=AMMS_e6e837c7bf3a77408619758b7447855a&amp;qlt=95</v>
     <v>38</v>
     <v>0</v>
@@ -5029,13 +5029,13 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1xzim&amp;q=XNAS%3aMSFT&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
+    <v>8</v>
+    <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
+    <v>10</v>
+    <v>11</v>
+    <v>Finance</v>
     <v>5</v>
-    <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>7</v>
-    <v>8</v>
-    <v>Finance</v>
-    <v>4</v>
     <v>en-US</v>
     <v>a1xzim</v>
     <v>268435456</v>
@@ -5043,9 +5043,9 @@
     <v>Powered by Refinitiv</v>
     <v>555.45000000000005</v>
     <v>349.2</v>
-    <v>1.1141000000000001</v>
-    <v>-3.19</v>
-    <v>-7.9299999999999995E-3</v>
+    <v>1.1227</v>
+    <v>-7.41</v>
+    <v>-1.8630000000000001E-2</v>
     <v>USD</v>
     <v>Microsoft Corporation is a technology company. The Company develops and supports software, services, devices, and solutions. The Company’s segments include Productivity and Business Processes, Intelligent Cloud, and More Personal Computing. The Productivity and Business Processes segment consists of products and services in its portfolio of productivity, communication, and information services. This segment primarily comprises: Office Commercial, Office Consumer, LinkedIn, and Dynamics business solutions. The Intelligent Cloud segment consists of server products and cloud services, including Azure and other cloud services, SQL Server, Windows Server, Visual Studio, System Center, and related Client Access Licenses (CALs), and Nuance and GitHub; and Enterprise Services, including enterprise support services, industry solutions and Nuance professional services. The More Personal Computing segment primarily comprises Windows, Devices, Gaming, and search and news advertising.</v>
     <v>228000</v>
@@ -5053,25 +5053,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Microsoft Way, REDMOND, WA, 98052 US</v>
-    <v>401.47</v>
+    <v>401</v>
     <v>39</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46224.664087453122</v>
+    <v>46225.999921921095</v>
     <v>40</v>
-    <v>396.32</v>
-    <v>2964688408500</v>
+    <v>386.96</v>
+    <v>2899615317900</v>
     <v>MICROSOFT CORPORATION</v>
     <v>MICROSOFT CORPORATION</v>
-    <v>399</v>
-    <v>23.770700000000001</v>
-    <v>402.29</v>
-    <v>399.1</v>
+    <v>399.58</v>
+    <v>23.248899999999999</v>
+    <v>397.75</v>
+    <v>390.34</v>
     <v>7428435000</v>
     <v>MSFT</v>
     <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>9807457</v>
-    <v>44237099</v>
+    <v>448169</v>
+    <v>43805283</v>
     <v>1993</v>
   </rv>
   <rv s="2">
@@ -5087,17 +5087,17 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1wzw7</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>692</v>
-    <v>410.11</v>
-    <v>0.1173</v>
-    <v>-4.8499999999999996</v>
-    <v>-9.5180000000000004E-3</v>
+    <v>411</v>
+    <v>0.1162</v>
+    <v>7.27</v>
+    <v>1.4336999999999999E-2</v>
     <v>USD</v>
     <v>Lockheed Martin Corporation is an aerospace and defense technology company. The Company's segments include Aeronautics, Missiles and Fire Control (MFC), Rotary and Mission Systems (RMS) and Space. The Aeronautics segment is engaged in research, design, development, manufacture, integration, sustainment, support and upgrade of advanced military aircraft, including combat and air mobility aircraft, unmanned air vehicles and related technologies. The MFC segment provides air and missile defense systems; tactical missiles and precision strike weapon systems; logistics; fire control systems; engineering support and integration services. The RMS segment designs, manufactures, services and supports various military and commercial helicopters, sea and land-based missile defense systems. The Space segment is engaged in the research and design, development, engineering and production of satellites, space transportation systems, and strategic, advanced strike, and defensive systems.</v>
     <v>123000</v>
@@ -5105,24 +5105,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>6801 ROCKLEDGE DR, BETHESDA, MD, 20817 US</v>
-    <v>506.5</v>
+    <v>521</v>
     <v>Aerospace &amp; Defense</v>
     <v>Stock</v>
-    <v>46224.664043587502</v>
+    <v>46225.999142962501</v>
     <v>43</v>
-    <v>487.15</v>
-    <v>116363143284</v>
+    <v>512</v>
+    <v>118592693296</v>
     <v>LOCKHEED MARTIN CORPORATION</v>
     <v>LOCKHEED MARTIN CORPORATION</v>
-    <v>501.91</v>
-    <v>24.441400000000002</v>
-    <v>509.54</v>
-    <v>504.69</v>
+    <v>515.79</v>
+    <v>24.909600000000001</v>
+    <v>507.09</v>
+    <v>514.36</v>
     <v>230563600</v>
     <v>LMT</v>
     <v>LOCKHEED MARTIN CORPORATION (XNYS:LMT)</v>
-    <v>501359</v>
-    <v>1260982</v>
+    <v>82545</v>
+    <v>1272464</v>
     <v>1994</v>
   </rv>
   <rv s="2">
@@ -5146,9 +5146,9 @@
     <v>Powered by Refinitiv</v>
     <v>421.6</v>
     <v>273.04000000000002</v>
-    <v>1.3693</v>
-    <v>7.27</v>
-    <v>1.9310000000000001E-2</v>
+    <v>1.3641000000000001</v>
+    <v>4.21</v>
+    <v>1.0993999999999999E-2</v>
     <v>USD</v>
     <v>Ralph Lauren Corporation is engaged in the design, marketing, and distribution of luxury lifestyle products, including apparel, footwear and accessories, home, fragrances and hospitality. Its segments include North America, Europe, and Asia. Its brands include Ralph Lauren, Ralph Lauren Collection, Ralph Lauren Purple Label, Polo Ralph Lauren, Lauren Ralph Lauren, Polo Ralph Lauren Children, and Chaps, among others. Its products include apparel and footwear and accessories for men, women, and children, as well as fragrance and home collections, together with its hospitality portfolio. Its range of footwear and accessories include casual shoes, dress shoes, boots, sneakers, sandals, eyewear, watches, scarves, hats and others. Its range of home products includes bed and bath lines, lighting, dining, floor coverings, giftware and more. Its hospitality collection is comprised of its restaurants, including The Polo Bar in New York City, RL Restaurant located in Chicago, and others.</v>
     <v>15600</v>
@@ -5156,24 +5156,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>650 Madison Ave, NEW YORK, NY, 10022 US</v>
-    <v>388.77</v>
+    <v>388.16</v>
     <v>Textiles &amp; Apparel</v>
     <v>Stock</v>
-    <v>46224.664053506247</v>
+    <v>46225.987667476562</v>
     <v>46</v>
-    <v>382.55</v>
-    <v>22839399312</v>
+    <v>381.62</v>
+    <v>23041159739</v>
     <v>RALPH LAUREN CORPORATION</v>
     <v>RALPH LAUREN CORPORATION</v>
-    <v>388.77</v>
-    <v>25.3964</v>
-    <v>376.48</v>
-    <v>383.75</v>
+    <v>383.37</v>
+    <v>25.620799999999999</v>
+    <v>382.93</v>
+    <v>387.14</v>
     <v>59516350</v>
     <v>RL</v>
     <v>RALPH LAUREN CORPORATION (XNYS:RL)</v>
-    <v>178050</v>
-    <v>690910</v>
+    <v>10</v>
+    <v>678311</v>
     <v>1997</v>
   </rv>
   <rv s="2">
@@ -5189,7 +5189,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1q6k2</v>
     <v>268435456</v>
@@ -5197,9 +5197,9 @@
     <v>Powered by Refinitiv</v>
     <v>1096.5</v>
     <v>844.06</v>
-    <v>0.87280000000000002</v>
-    <v>-6.335</v>
-    <v>-6.7700000000000008E-3</v>
+    <v>0.87409999999999999</v>
+    <v>-1.91</v>
+    <v>-2.055E-3</v>
     <v>USD</v>
     <v>Costco Wholesale Corporation (Costco) operates membership warehouses and e-commerce sites that offer a selection of nationally branded and private-label products in a wide range of categories. The Company buys the majority of its merchandise directly from suppliers and route it to cross-docking consolidation points (depots) or directly to its warehouses. It operates 891 warehouses, including 614 in the United States and Puerto Rico, 108 in Canada, 40 in Mexico, 35 in Japan, 29 in the United Kingdom, 19 in Korea, 15 in Australia, 14 in Taiwan, seven in China, five in Spain, two in France, and one each in Iceland, New Zealand and Sweden. It also operates e-commerce sites in the United States, Canada, the United Kingdom, Mexico, Korea, Taiwan, Japan and Australia. The Company provides wide selection of merchandise, plus the convenience of specialty departments and exclusive member services.</v>
     <v>341000</v>
@@ -5207,24 +5207,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>999 Lake Dr, ISSAQUAH, WA, 98027- US</v>
-    <v>931.97</v>
+    <v>933.6</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46224.664073599219</v>
+    <v>46225.999897325783</v>
     <v>49</v>
-    <v>924.44</v>
-    <v>412198022842</v>
+    <v>920.96500000000003</v>
+    <v>411242326028</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
-    <v>931</v>
-    <v>46.748600000000003</v>
-    <v>935.8</v>
-    <v>929.46500000000003</v>
+    <v>930.88</v>
+    <v>46.640300000000003</v>
+    <v>929.22</v>
+    <v>927.31</v>
     <v>443478800</v>
     <v>COST</v>
     <v>COSTCO WHOLESALE CORPORATION (XNAS:COST)</v>
-    <v>530345</v>
-    <v>2633532</v>
+    <v>6555</v>
+    <v>2637364</v>
     <v>1987</v>
   </rv>
   <rv s="2">
@@ -5234,12 +5234,12 @@
     <v>http://en.wikipedia.org/wiki/The_Walt_Disney_Company</v>
     <v>Wikipedia</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>30</v>
     <v>52</v>
   </rv>
-  <rv s="4">
-    <v>9</v>
+  <rv s="5">
+    <v>12</v>
     <v>https://www.bing.com/th?id=AMMS_0aa288ba528f6f45e3de87d97e250136&amp;qlt=95</v>
     <v>53</v>
     <v>0</v>
@@ -5250,13 +5250,13 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1r2z2&amp;q=XNYS%3aDIS&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
+    <v>8</v>
+    <v>THE WALT DISNEY COMPANY (XNYS:DIS)</v>
+    <v>10</v>
+    <v>11</v>
+    <v>Finance</v>
     <v>5</v>
-    <v>THE WALT DISNEY COMPANY (XNYS:DIS)</v>
-    <v>7</v>
-    <v>8</v>
-    <v>Finance</v>
-    <v>4</v>
     <v>en-US</v>
     <v>a1r2z2</v>
     <v>268435456</v>
@@ -5264,9 +5264,9 @@
     <v>Powered by Refinitiv</v>
     <v>123.4</v>
     <v>92.185000000000002</v>
-    <v>1.3937999999999999</v>
-    <v>-0.01</v>
-    <v>-1.0370000000000001E-4</v>
+    <v>1.397</v>
+    <v>-0.27</v>
+    <v>-2.8079999999999997E-3</v>
     <v>USD</v>
     <v>The Walt Disney Company is a diversified worldwide entertainment company. The Company's segments include Entertainment, Sports and Experiences. The Entertainment segment generally encompasses its non-sports focused global film and episodic content production and distribution activities. The lines of business within the Entertainment segment along with their business activities include Linear Networks, Direct-to-Consumer, and Content Sales/Licensing. The Sports segment encompasses its sports-focused global television and direct-to-consumer (DTC) video streaming content production and distribution activities. The lines of business within the Sports segment include ESPN and Star. The Experiences segment includes Parks and Experiences and Consumer Products. Parks and Experiences consists of Walt Disney World Resort in Florida, Disneyland Resort in California, Disney Cruise Line, and others. Consumer Products includes licensing of its trade names, characters, visual, literary and other IP.</v>
     <v>231000</v>
@@ -5274,25 +5274,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>500 South Buena Vista Street, BURBANK, CA, 91521-0001 US</v>
-    <v>96.885000000000005</v>
+    <v>97.3</v>
     <v>54</v>
     <v>Media &amp; Publishing</v>
     <v>Stock</v>
-    <v>46224.664078726564</v>
+    <v>46225.999659293753</v>
     <v>55</v>
-    <v>95.87</v>
-    <v>167399660400</v>
+    <v>95.644999999999996</v>
+    <v>166479309570</v>
     <v>THE WALT DISNEY COMPANY</v>
     <v>THE WALT DISNEY COMPANY</v>
-    <v>95.99</v>
-    <v>15.426</v>
-    <v>96.41</v>
-    <v>96.4</v>
+    <v>97.12</v>
+    <v>15.341200000000001</v>
+    <v>96.14</v>
+    <v>95.87</v>
     <v>1736511000</v>
     <v>DIS</v>
     <v>THE WALT DISNEY COMPANY (XNYS:DIS)</v>
-    <v>3341755</v>
-    <v>11415592</v>
+    <v>30469</v>
+    <v>11475119</v>
     <v>2018</v>
   </rv>
   <rv s="2">
@@ -5308,7 +5308,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1slm7</v>
     <v>268435456</v>
@@ -5316,9 +5316,9 @@
     <v>Powered by Refinitiv</v>
     <v>796.25</v>
     <v>520.26</v>
-    <v>1.2248000000000001</v>
-    <v>2.625</v>
-    <v>4.0639999999999999E-3</v>
+    <v>1.2373000000000001</v>
+    <v>-16.64</v>
+    <v>-2.5846000000000001E-2</v>
     <v>USD</v>
     <v>Meta Platforms, Inc. is building human connections, powered by artificial intelligence and immersive technologies. The Company's products enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) and mixed reality (MR) headsets, augmented reality (AR), and wearables. It also helps people discover and learn about what is going on in the world around them, enabling people to share their experiences, ideas, photos, videos, and other content with audiences ranging from their closest family members and friends to the public at large. The Company's segments include Family of Apps (FoA) and Reality Labs (RL). FoA segment includes Facebook, Instagram, Messenger, WhatsApp and Threads. RL segment includes its virtual, augmented, and mixed reality related consumer hardware, software and content. Its product offerings in VR include its Meta Quest devices, as well as software and content available through the Meta Horizon Store.</v>
     <v>77986</v>
@@ -5326,24 +5326,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1 Meta Way, MENLO PARK, CA, 94025 US</v>
-    <v>655.88</v>
+    <v>648.99800000000005</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46224.664072626561</v>
+    <v>46225.999996712497</v>
     <v>58</v>
-    <v>643.20000000000005</v>
-    <v>1646103854925</v>
+    <v>624</v>
+    <v>1592022752910</v>
     <v>META PLATFORMS, INC.</v>
     <v>META PLATFORMS, INC.</v>
-    <v>654.17999999999995</v>
-    <v>19.6692</v>
-    <v>645.85</v>
-    <v>648.47500000000002</v>
+    <v>647.70000000000005</v>
+    <v>19.023</v>
+    <v>643.80999999999995</v>
+    <v>627.16999999999996</v>
     <v>2538423000</v>
     <v>META</v>
     <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>2686417</v>
-    <v>19691910</v>
+    <v>272326</v>
+    <v>19483618</v>
     <v>2004</v>
   </rv>
   <rv s="2">
@@ -5359,7 +5359,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a269ec</v>
     <v>268435456</v>
@@ -5367,9 +5367,9 @@
     <v>Powered by Refinitiv</v>
     <v>176.41</v>
     <v>105.52500000000001</v>
-    <v>0.1628</v>
-    <v>2.7250000000000001</v>
-    <v>1.8367000000000001E-2</v>
+    <v>0.16339999999999999</v>
+    <v>2.74</v>
+    <v>1.8061000000000001E-2</v>
     <v>USD</v>
     <v>ExxonMobil Holdings Corporation is a holding company whose direct, wholly owned subsidiary and principal operating company is Exxon Mobil Corporation. Its principal business involves exploration and production of crude oil and natural gas; manufacture, trade, transport and sale of crude oil, natural gas, petroleum products, petrochemicals, and a wide variety of specialty products; and pursuit of lower-emission and other new business opportunities, including carbon capture and storage, hydrogen and ammonia, lower-emission fuels, Proxxima resin systems, carbon materials, low-carbon data centers, and lithium. Affiliates of the Company conduct research programs in support of these businesses. It operates or markets its products in the United States and most other countries of the world. Its Upstream businesses include unconventional, conventional, deepwater, heavy oil and liquefied natural gas. It also manufactures and distributes products derived from crude oil and other feedstocks.</v>
     <v>58000</v>
@@ -5377,24 +5377,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>22777 SPRINGWOODS VILLAGE PKWY, SPRING, TX, 77389-1425 US</v>
-    <v>151.49</v>
+    <v>154.80000000000001</v>
     <v>Oil &amp; Gas</v>
     <v>Stock</v>
-    <v>46224.664100647657</v>
+    <v>46225.999640728907</v>
     <v>61</v>
-    <v>148.47999999999999</v>
-    <v>626239317495</v>
+    <v>152.94999999999999</v>
+    <v>640187064150</v>
     <v>Exxonmobil Holdings Corp</v>
     <v>Exxonmobil Holdings Corp</v>
-    <v>148.99</v>
-    <v>25.5565</v>
-    <v>148.36000000000001</v>
-    <v>151.08500000000001</v>
+    <v>153.86000000000001</v>
+    <v>26.125900000000001</v>
+    <v>151.71</v>
+    <v>154.44999999999999</v>
     <v>4144947000</v>
     <v>XOM</v>
     <v>Exxonmobil Holdings Corp (XNYS:XOM)</v>
-    <v>4349227</v>
-    <v>17490945</v>
+    <v>250475</v>
+    <v>17308230</v>
     <v>2026</v>
   </rv>
   <rv s="2">
@@ -5410,7 +5410,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1y4oc</v>
     <v>268435456</v>
@@ -5418,9 +5418,9 @@
     <v>Powered by Refinitiv</v>
     <v>1255</v>
     <v>103.38</v>
-    <v>2.1983000000000001</v>
-    <v>87.867900000000006</v>
-    <v>0.10152699999999999</v>
+    <v>2.1768000000000001</v>
+    <v>-11.34</v>
+    <v>-1.1680999999999999E-2</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -5428,24 +5428,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>958.5</v>
+    <v>982.62</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46224.66409428203</v>
+    <v>46225.999990231248</v>
     <v>64</v>
-    <v>916.57010000000002</v>
-    <v>1076681856964</v>
+    <v>936.06</v>
+    <v>1083629995640</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>925.83</v>
-    <v>21.582100000000001</v>
-    <v>865.46</v>
-    <v>953.3279</v>
+    <v>938.25</v>
+    <v>21.721399999999999</v>
+    <v>970.82</v>
+    <v>959.48</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>23076024</v>
-    <v>51373126</v>
+    <v>1563004</v>
+    <v>51708072</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -5461,7 +5461,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>bwvem7</v>
     <v>268435456</v>
@@ -5469,9 +5469,9 @@
     <v>Powered by Refinitiv</v>
     <v>150.88</v>
     <v>110.81</v>
-    <v>1.1466000000000001</v>
-    <v>-0.74</v>
-    <v>-5.1060000000000003E-3</v>
+    <v>1.1516999999999999</v>
+    <v>-4.05</v>
+    <v>-2.8105000000000002E-2</v>
     <v>USD</v>
     <v>Airbnb, Inc. operates a global platform for stays and experiences. The Company’s marketplace model connects hosts and guests online or through mobile devices to book spaces and experiences around the world. The Company has built its platform to onboard new hosts, especially those who previously had not considered hosting. It partners with hosts throughout the process of setting up their listing and provides them with a suite of tools to manage their listings, including scheduling, merchandising, integrated payments, community support, host protection, pricing guidance, and feedback from reviews. Its Website and mobile applications provide its guests with a way to explore a variety of homes and experiences and an easy way to book them. Its technology platform powers its two-sided marketplace and enables its global network of hosts and guests. It owns a trademark portfolio with protection in 220 countries in which it operates for its primary brands, AIRBNB, and its Belo logo.</v>
     <v>8200</v>
@@ -5479,24 +5479,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>888 Brannan St., SAN FRANCISCO, CA, 94103 US</v>
-    <v>145.62</v>
+    <v>144.47</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46224.664078205467</v>
+    <v>46225.996556573438</v>
     <v>67</v>
-    <v>143.31</v>
-    <v>85583406580</v>
+    <v>139.69</v>
+    <v>83120361245</v>
     <v>AIRBNB, INC.</v>
     <v>AIRBNB, INC.</v>
-    <v>144.78</v>
-    <v>35.5321</v>
-    <v>144.94</v>
-    <v>144.19999999999999</v>
+    <v>144.1</v>
+    <v>34.509900000000002</v>
+    <v>144.1</v>
+    <v>140.05000000000001</v>
     <v>593504900</v>
     <v>ABNB</v>
     <v>AIRBNB, INC. (XNAS:ABNB)</v>
-    <v>485790</v>
-    <v>3782582</v>
+    <v>1476</v>
+    <v>3771674</v>
     <v>2008</v>
   </rv>
   <rv s="2">
@@ -5512,7 +5512,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>brg5u2</v>
     <v>268435456</v>
@@ -5520,9 +5520,9 @@
     <v>Powered by Refinitiv</v>
     <v>70.430000000000007</v>
     <v>13.74</v>
-    <v>2.3881000000000001</v>
-    <v>0.20499999999999999</v>
-    <v>6.2690000000000003E-3</v>
+    <v>2.3875999999999999</v>
+    <v>-1.05</v>
+    <v>-3.2080999999999998E-2</v>
     <v>USD</v>
     <v>Hims &amp; Hers Health, Inc. operates as a consumer-first platform, which helps customers to fulfill their health and wellness needs. Its platform includes access to a provider network, a clinically focused electronic medical record system, digital prescriptions, cloud-enabled pharmacy fulfillment, and personalization capabilities. Its digital platform enables access to treatments for a range of conditions, including primarily those related to sexual health, hair loss, hormone health, weight loss, dermatology, and mental health, as well as services such as comprehensive laboratory testing. It connects patients to licensed healthcare professionals who can prescribe medications when appropriate and prescriptions are fulfilled online through licensed pharmacies. It also offers access to a range of health and wellness products designed to meet individual needs, which can include curated prescription and non-prescription products.</v>
     <v>2442</v>
@@ -5530,24 +5530,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>2269 Chestnut St, #523, SAN FRANCISCO, CA, 94123 US</v>
-    <v>33.840000000000003</v>
+    <v>34</v>
     <v>Healthcare Providers &amp; Services</v>
     <v>Stock</v>
-    <v>46224.664085265627</v>
+    <v>46225.999970925783</v>
     <v>70</v>
-    <v>32.100099999999998</v>
-    <v>7616115618</v>
+    <v>31.4499</v>
+    <v>7332579936</v>
     <v>HIMS &amp; HERS HEALTH, INC.</v>
     <v>HIMS &amp; HERS HEALTH, INC.</v>
-    <v>32.33</v>
+    <v>33.450000000000003</v>
     <v>0</v>
-    <v>32.700000000000003</v>
-    <v>32.905000000000001</v>
+    <v>32.729999999999997</v>
+    <v>31.68</v>
     <v>231457700</v>
     <v>HIMS</v>
     <v>HIMS &amp; HERS HEALTH, INC. (XNYS:HIMS)</v>
-    <v>2762997</v>
-    <v>16031832</v>
+    <v>64510</v>
+    <v>15660187</v>
     <v>2021</v>
   </rv>
   <rv s="2">
@@ -5563,7 +5563,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1r4dm</v>
     <v>268435456</v>
@@ -5571,9 +5571,9 @@
     <v>Powered by Refinitiv</v>
     <v>244.38</v>
     <v>186.67</v>
-    <v>1.2131000000000001</v>
-    <v>-5.6150000000000002</v>
-    <v>-2.6199E-2</v>
+    <v>1.2121999999999999</v>
+    <v>1.72</v>
+    <v>8.2529999999999999E-3</v>
     <v>USD</v>
     <v>DICK'S Sporting Goods, Inc. is an omni-channel sporting goods retailer. The Company owns and operates Golf Galaxy, Public Lands, and Going Going Gone! specialty concept stores, and also offers its products online and through its mobile applications. It also owns and operates DICK’S House of Sport and Golf Galaxy Performance Center, as well as GameChanger, a youth sports mobile platform for livestreaming, scheduling, communications and scorekeeping. The Company operates over 3,200 stores e-commerce and digital businesses across 20 countries in North America, Europe, Asia, and Australia, plus a licensed store presence in Europe, the Middle East and Asia. It carries a wide variety of national brands, including but not limited to adidas, Asics, Brooks, Callaway Golf, Carhartt, Columbia, Hoka, Jordan, New Balance, Nike, Peloton, The North Face, Under Armour, Wilson, Yeti, and others. It also owns and operates brands such as Foot Locker, Kids Foot Locker, Champs Sports, WSS, and atmos.</v>
     <v>31600</v>
@@ -5581,24 +5581,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>345 Court Street, CORAOPOLIS, PA, 15108 US</v>
-    <v>214.47</v>
+    <v>210.25</v>
     <v>Specialty Retailers</v>
     <v>Stock</v>
-    <v>46224.663938657031</v>
+    <v>46225.981994664064</v>
     <v>73</v>
-    <v>208.7</v>
-    <v>18679627610</v>
+    <v>206.54</v>
+    <v>18807168730</v>
     <v>DICK'S SPORTING GOODS, INC.</v>
     <v>DICK'S SPORTING GOODS, INC.</v>
-    <v>214.32</v>
-    <v>19.837399999999999</v>
-    <v>214.32</v>
-    <v>208.70500000000001</v>
+    <v>209.44</v>
+    <v>19.972799999999999</v>
+    <v>208.41</v>
+    <v>210.13</v>
     <v>89502540</v>
     <v>DKS</v>
     <v>DICK'S SPORTING GOODS, INC. (XNYS:DKS)</v>
-    <v>294528</v>
-    <v>1155908</v>
+    <v>913</v>
+    <v>1161468</v>
     <v>1996</v>
   </rv>
   <rv s="2">
@@ -5608,12 +5608,12 @@
     <v>http://pt.wikipedia.org/wiki/Oracle_Corporation</v>
     <v>Wikipedia</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>30</v>
     <v>76</v>
   </rv>
-  <rv s="4">
-    <v>9</v>
+  <rv s="5">
+    <v>12</v>
     <v>https://www.bing.com/th?id=AMMS_672116c618c664d13b2515d6587ba357&amp;qlt=95</v>
     <v>77</v>
     <v>0</v>
@@ -5624,13 +5624,13 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1zbec&amp;q=XNYS%3aORCL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
+    <v>8</v>
+    <v>ORACLE CORPORATION (XNYS:ORCL)</v>
+    <v>10</v>
+    <v>11</v>
+    <v>Finance</v>
     <v>5</v>
-    <v>ORACLE CORPORATION (XNYS:ORCL)</v>
-    <v>7</v>
-    <v>8</v>
-    <v>Finance</v>
-    <v>4</v>
     <v>en-US</v>
     <v>a1zbec</v>
     <v>268435456</v>
@@ -5638,9 +5638,9 @@
     <v>Powered by Refinitiv</v>
     <v>345.72</v>
     <v>120.03</v>
-    <v>1.7263999999999999</v>
-    <v>3.69</v>
-    <v>3.04E-2</v>
+    <v>1.7155</v>
+    <v>-1.21</v>
+    <v>-9.5239999999999995E-3</v>
     <v>USD</v>
     <v>Oracle Corporation offers integrated suites of applications plus secure, autonomous infrastructure in the Oracle Cloud. The Company operates through three businesses: cloud and license, hardware and service. Its cloud and license business is engaged in the sale, marketing and delivery of its enterprise applications and infrastructure technologies through cloud and on-premise deployment models including its cloud services and license support offerings, and its cloud license and on-premise license offerings. Its hardware business provides infrastructure technologies including Oracle Engineered Systems, servers, storage, industry-specific hardware, operating systems, virtualization, management and other hardware-related software to support diverse IT environments. Its services business provides services to customers and partners to help maximize the performance of their investments in Oracle applications and infrastructure technologies.</v>
     <v>141000</v>
@@ -5648,25 +5648,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>2300 Oracle Way, AUSTIN, TX, 78741 US</v>
-    <v>126.2</v>
+    <v>128.84</v>
     <v>78</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46224.664085358592</v>
+    <v>46225.999981816407</v>
     <v>79</v>
-    <v>122.21</v>
-    <v>360260507970</v>
+    <v>124.7</v>
+    <v>362478470640</v>
     <v>ORACLE CORPORATION</v>
     <v>ORACLE CORPORATION</v>
-    <v>122.63</v>
-    <v>20.349799999999998</v>
-    <v>121.38</v>
-    <v>125.07</v>
+    <v>126.18</v>
+    <v>20.475100000000001</v>
+    <v>127.05</v>
+    <v>125.84</v>
     <v>2880471000</v>
     <v>ORCL</v>
     <v>ORACLE CORPORATION (XNYS:ORCL)</v>
-    <v>10656681</v>
-    <v>36649915</v>
+    <v>275482</v>
+    <v>36577347</v>
     <v>2005</v>
   </rv>
   <rv s="2">
@@ -5682,7 +5682,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1ygoc</v>
     <v>268435456</v>
@@ -5690,9 +5690,9 @@
     <v>Powered by Refinitiv</v>
     <v>126.71</v>
     <v>65.08</v>
-    <v>1.5286999999999999</v>
-    <v>-0.2</v>
-    <v>-2.9589999999999998E-3</v>
+    <v>1.5261</v>
+    <v>-0.14000000000000001</v>
+    <v>-2.039E-3</v>
     <v>USD</v>
     <v>Netflix, Inc. is a provider of entertainment services. The Company acquires, licenses and produces content, including original programming. It provides paid memberships in over 190 countries offering television (TV) series, films and games across a variety of genres and languages. It allows members to play, pause and resume watching as much as they want, anytime, anywhere, and can change their plans at any time. The Company offers members the ability to receive streaming content through a host of Internet-connected devices, including TVs, digital video players, TV set-top boxes and mobile devices. It is engaged in scaling its streaming service, such as introducing games and advertising on its service, as well as offering live programming. It is developing technology and utilizing third-party cloud computing, technology and other services. The Company is also engaged in scaling its own studio operations to produce original content.</v>
     <v>16000</v>
@@ -5700,24 +5700,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Albright Way, LOS GATOS, CA, 95032 US</v>
-    <v>68.099999999999994</v>
+    <v>70.569999999999993</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46224.66408313594</v>
+    <v>46225.999973935155</v>
     <v>82</v>
-    <v>67.17</v>
-    <v>280649488600</v>
+    <v>68.349999999999994</v>
+    <v>285354739670</v>
     <v>NETFLIX, INC.</v>
     <v>NETFLIX, INC.</v>
-    <v>67.489999999999995</v>
-    <v>21.233699999999999</v>
-    <v>67.599999999999994</v>
-    <v>67.400000000000006</v>
+    <v>69.37</v>
+    <v>21.589400000000001</v>
+    <v>68.67</v>
+    <v>68.53</v>
     <v>4163939000</v>
     <v>NFLX</v>
     <v>NETFLIX, INC. (XNAS:NFLX)</v>
-    <v>17646944</v>
-    <v>53916188</v>
+    <v>282459</v>
+    <v>54765053</v>
     <v>1997</v>
   </rv>
   <rv s="2">
@@ -5733,7 +5733,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1o4ec</v>
     <v>268435456</v>
@@ -5741,9 +5741,9 @@
     <v>Powered by Refinitiv</v>
     <v>254.34989999999999</v>
     <v>176.77</v>
-    <v>1.2151000000000001</v>
-    <v>1.66</v>
-    <v>7.9240000000000005E-3</v>
+    <v>1.2152000000000001</v>
+    <v>3.85</v>
+    <v>1.8799E-2</v>
     <v>USD</v>
     <v>The Boeing Company is an aerospace company. Its segments include Commercial Airplanes (BCA), Defense, Space &amp; Security (BDS), and Global Services (BGS). Its BCA segment develops, produces and markets commercial jet aircraft principally for the commercial airline industry worldwide. Its family of commercial jet aircraft in production includes the 737 narrow-body model and the 767, 777 and 787 wide-body models. Its BDS segment is engaged in the research, development, production and modification of manned and unmanned military aircraft and weapons systems for strike, surveillance and mobility. Its BGS segment provides services to its commercial and defense customers worldwide. It sustains aerospace platforms and systems with a range of products and services, including supply chain and logistics management, engineering, maintenance and modifications, upgrades and conversions, spare parts, pilot and maintenance training systems and services, technical and maintenance documents, and others.</v>
     <v>182000</v>
@@ -5751,24 +5751,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>929 Long Bridge Drive, ARLINGTON, VA, 22202 US</v>
-    <v>211.7</v>
+    <v>209.25</v>
     <v>Aerospace &amp; Defense</v>
     <v>Stock</v>
-    <v>46224.664061284377</v>
+    <v>46225.997994883597</v>
     <v>85</v>
-    <v>207.2</v>
-    <v>166442147622</v>
+    <v>204.88</v>
+    <v>164479274895</v>
     <v>THE BOEING COMPANY</v>
     <v>THE BOEING COMPANY</v>
-    <v>209.745</v>
-    <v>92.964100000000002</v>
-    <v>209.48</v>
-    <v>211.14</v>
+    <v>205</v>
+    <v>91.866100000000003</v>
+    <v>204.8</v>
+    <v>208.65</v>
     <v>788302300</v>
     <v>BA</v>
     <v>THE BOEING COMPANY (XNYS:BA)</v>
-    <v>1839621</v>
-    <v>5387413</v>
+    <v>26097</v>
+    <v>5562298</v>
     <v>1934</v>
   </rv>
   <rv s="2">
@@ -5784,7 +5784,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1xxmw</v>
     <v>268435456</v>
@@ -5792,9 +5792,9 @@
     <v>Powered by Refinitiv</v>
     <v>131.74</v>
     <v>76.66</v>
-    <v>0.21299999999999999</v>
-    <v>0.89</v>
-    <v>7.1540000000000006E-3</v>
+    <v>0.20880000000000001</v>
+    <v>1.21</v>
+    <v>9.5830000000000012E-3</v>
     <v>USD</v>
     <v>Merck &amp; Co., Inc. is a global health care company that delivers health solutions through its prescription medicines, including biologic therapies, vaccines and animal health products. Its Pharmaceutical segment includes human health pharmaceutical and vaccine products. The Company sells its human health pharmaceutical products primarily to drug wholesalers and retailers, hospitals, government agencies and managed health care providers. It sells these human health vaccines primarily to physicians, wholesalers, distributors and government entities. Its Animal Health segment discovers, develops, manufactures and markets a range of veterinary pharmaceutical and vaccine products, as well as health management solutions and services, for the prevention, treatment and control of disease in all livestock and companion animal species. Its products include KEYTRUDA (pembrolizumab) injection, for intravenous use; WELIREG (belzutifan) tablets, for oral use; Ohtuvayre (ensifentrine) and others.</v>
     <v>75000</v>
@@ -5802,24 +5802,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>126 East Lincoln Avenue, P.O. Box 2000, RAHWAY, NJ, 07065 US</v>
-    <v>126.77</v>
+    <v>128.83000000000001</v>
     <v>Pharmaceuticals</v>
     <v>Stock</v>
-    <v>46224.664078390626</v>
+    <v>46225.999670844532</v>
     <v>88</v>
-    <v>124.095</v>
-    <v>309444248960</v>
+    <v>126.6208</v>
+    <v>314828465280</v>
     <v>MERCK &amp; CO., INC.</v>
     <v>MERCK &amp; CO., INC.</v>
-    <v>124.4</v>
-    <v>35.251300000000001</v>
-    <v>124.4</v>
-    <v>125.29</v>
+    <v>127.32</v>
+    <v>35.865099999999998</v>
+    <v>126.26</v>
+    <v>127.47</v>
     <v>2469824000</v>
     <v>MRK</v>
     <v>MERCK &amp; CO., INC. (XNYS:MRK)</v>
-    <v>2886858</v>
-    <v>11311915</v>
+    <v>6595</v>
+    <v>11168622</v>
     <v>1970</v>
   </rv>
   <rv s="2">
@@ -5835,7 +5835,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1yv52</v>
     <v>268435456</v>
@@ -5843,9 +5843,9 @@
     <v>Powered by Refinitiv</v>
     <v>236.54</v>
     <v>164.07</v>
-    <v>2.2206999999999999</v>
-    <v>2.76</v>
-    <v>1.3576999999999999E-2</v>
+    <v>2.2187999999999999</v>
+    <v>4.7699999999999996</v>
+    <v>2.3011E-2</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -5853,24 +5853,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>208.65</v>
+    <v>214.39</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46224.664090370316</v>
+    <v>46225.999992950783</v>
     <v>91</v>
-    <v>204.01009999999999</v>
-    <v>4986168000000</v>
+    <v>204.95</v>
+    <v>5131852000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>207.7</v>
-    <v>31.552800000000001</v>
-    <v>203.28</v>
-    <v>206.04</v>
+    <v>205.80500000000001</v>
+    <v>32.474899999999998</v>
+    <v>207.29</v>
+    <v>212.06</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>44409630</v>
-    <v>140236146</v>
+    <v>1369474</v>
+    <v>140089756</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -5886,7 +5886,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1ntlh</v>
     <v>268435456</v>
@@ -5894,9 +5894,9 @@
     <v>Powered by Refinitiv</v>
     <v>1999.96</v>
     <v>683.48</v>
-    <v>1.7917000000000001</v>
-    <v>73.995000000000005</v>
-    <v>4.2549999999999998E-2</v>
+    <v>1.7833000000000001</v>
+    <v>0.35</v>
+    <v>1.9430000000000001E-4</v>
     <v>USD</v>
     <v>ASML Holding N.V. is a holding company based in the Netherlands. The Company operates through its subsidiaries in the Netherlands, the United States, Italy, France, Germany, the United Kingdom, Ireland, Belgium, South Korea, Taiwan, Singapore, China, Hong Kong, Japan, Malaysia and Israel. The Company operates through one business segment which is engage in development, production, marketing, sales, upgrading and servicing of advanced semiconductor equipment systems, consisting of lithography, metrology and inspection systems. The Company offers TWINSCAN systems, equipped with lithography system with a mercury lamp as light source (i-line), Krypton Fluoride (KrF) and Argon Fluoride (ArF) light sources for processing wafers for manufacturing environments for which imaging at a small resolution is required. TWINSCAN systems also include immersion lithography systems (TWINSCAN immersion systems).</v>
     <v>43938</v>
@@ -5904,24 +5904,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>De Run 6501, VELDHOVEN, NOORD-BRABANT, 5504 DR NL</v>
-    <v>1821.75</v>
+    <v>1817.2</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46224.664090659375</v>
+    <v>46225.999818008597</v>
     <v>94</v>
-    <v>1785.54</v>
-    <v>703717602315</v>
+    <v>1767.04</v>
+    <v>699387814722</v>
     <v>ASML Holding NV</v>
     <v>ASML Holding NV</v>
-    <v>1800</v>
-    <v>59.860399999999998</v>
-    <v>1739.02</v>
-    <v>1813.0150000000001</v>
+    <v>1767.65</v>
+    <v>59.492100000000001</v>
+    <v>1801.51</v>
+    <v>1801.86</v>
     <v>388147700</v>
     <v>ASML</v>
     <v>ASML Holding NV (XNAS:ASML)</v>
-    <v>773286</v>
-    <v>2200000</v>
+    <v>24303</v>
+    <v>2165990</v>
     <v>1994</v>
   </rv>
   <rv s="2">
@@ -5931,13 +5931,13 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33k6h&amp;q=S%26P+500+INDEX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
-    <v>10</v>
+  <rv s="7">
+    <v>13</v>
     <v>S&amp;P 500 INDEX</v>
-    <v>11</v>
-    <v>12</v>
+    <v>14</v>
+    <v>15</v>
     <v>Finance</v>
-    <v>13</v>
+    <v>16</v>
     <v>en-US</v>
     <v>a33k6h</v>
     <v>268435456</v>
@@ -5945,17 +5945,17 @@
     <v>Powered by Refinitiv</v>
     <v>7620.9</v>
     <v>6212.69</v>
-    <v>58.15</v>
-    <v>7.8120000000000004E-3</v>
+    <v>-10.24</v>
+    <v>-1.364E-3</v>
     <v>DE</v>
-    <v>7505.15</v>
+    <v>7525.94</v>
     <v>Index</v>
     <v>97</v>
-    <v>7467.86</v>
+    <v>7485.85</v>
     <v>S&amp;P 500 INDEX</v>
-    <v>7489.95</v>
-    <v>7443.28</v>
-    <v>7501.43</v>
+    <v>7497.47</v>
+    <v>7509.2</v>
+    <v>7498.96</v>
     <v>INX</v>
     <v>S&amp;P 500 INDEX</v>
   </rv>
@@ -5972,7 +5972,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1mou2</v>
     <v>268435456</v>
@@ -5980,9 +5980,9 @@
     <v>Powered by Refinitiv</v>
     <v>334.99</v>
     <v>201.5</v>
-    <v>1.0744</v>
-    <v>2.2749999999999999</v>
-    <v>6.966E-3</v>
+    <v>1.0831999999999999</v>
+    <v>-1.85</v>
+    <v>-5.6449999999999998E-3</v>
     <v>USD</v>
     <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
@@ -5990,30 +5990,30 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Apple Park Way, CUPERTINO, CA, 95014 US</v>
-    <v>328.98</v>
+    <v>328.99950000000001</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46224.664098263282</v>
+    <v>46225.999879536721</v>
     <v>100</v>
-    <v>322.22039999999998</v>
-    <v>4830158646400</v>
+    <v>323.33999999999997</v>
+    <v>4786463750400</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
-    <v>323.14</v>
-    <v>39.940899999999999</v>
-    <v>326.58999999999997</v>
-    <v>328.86500000000001</v>
+    <v>327.87</v>
+    <v>39.5794</v>
+    <v>327.74</v>
+    <v>325.89</v>
     <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>15240812</v>
-    <v>62770043</v>
+    <v>360981</v>
+    <v>62872208</v>
     <v>1977</v>
   </rv>
   <rv s="2">
     <v>101</v>
   </rv>
-  <rv s="7">
+  <rv s="8">
     <v>12</v>
     <v>Price</v>
     <v>0</v>
@@ -6026,9 +6026,9 @@
     <v>0</v>
     <v>ASICS Corporation (OTCM:ASCCY)</v>
     <v>2</v>
-    <v>14</v>
+    <v>17</v>
     <v>Finance</v>
-    <v>15</v>
+    <v>18</v>
     <v>en-US</v>
     <v>a28i3m</v>
     <v>268435456</v>
@@ -6036,9 +6036,9 @@
     <v>Powered by Refinitiv</v>
     <v>31.99</v>
     <v>22.2</v>
-    <v>1.3665</v>
-    <v>-0.4975</v>
-    <v>-1.6303000000000002E-2</v>
+    <v>1.3691</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>ASICS Corporation is a Japan-based company mainly engaged in the manufacture and sale of sports products, such as sports shoes, sportswear, sports equipment and others. The Company operates through six business segments. The Japan Region, Americas Region, Europe Region (including the Middle East and Africa), Oceania/Southeast and South Asia Region, and the East Asia Region segment mainly sell sporting goods. The Others segment is engaged in the manufacture and sale of HAGLOFS brand outdoor products.</v>
     <v>9455</v>
@@ -6046,24 +6046,24 @@
     <v>OTCM</v>
     <v>OTCM</v>
     <v>Yamato Kobe Bldg., 1-2-4, Sannomiya-cho, Chuo-ku, KOBE-SHI, HYOGO-KEN, 650-0021 JP</v>
-    <v>30.04</v>
+    <v>29.18</v>
     <v>Textiles &amp; Apparel</v>
     <v>Stock</v>
-    <v>46224.653263842185</v>
+    <v>46226.006944444445</v>
     <v>104</v>
-    <v>29.79</v>
-    <v>3595291000000</v>
+    <v>29.024999999999999</v>
+    <v>3490994000000</v>
     <v>ASICS Corporation</v>
     <v>ASICS Corporation</v>
-    <v>29.88</v>
+    <v>29.18</v>
     <v>0</v>
-    <v>30.515000000000001</v>
-    <v>30.017499999999998</v>
+    <v>29.06</v>
+    <v>29.06</v>
     <v>734482200</v>
     <v>ASCCY</v>
     <v>ASICS Corporation (OTCM:ASCCY)</v>
-    <v>16152</v>
-    <v>3356010</v>
+    <v>14896</v>
+    <v>3180730</v>
     <v>1943</v>
   </rv>
   <rv s="2">
@@ -6087,9 +6087,9 @@
     <v>Powered by Refinitiv</v>
     <v>53.25</v>
     <v>37.76</v>
-    <v>0.79679999999999995</v>
-    <v>-0.86</v>
-    <v>-1.6787E-2</v>
+    <v>0.79900000000000004</v>
+    <v>-0.14000000000000001</v>
+    <v>-2.784E-3</v>
     <v>USD</v>
     <v>Atlanta Braves Holdings, Inc. is a holding company of Braves Holdings, LLC (Braves Holdings). Braves Holdings is the owner and operator of the Atlanta Braves Major League Baseball Club and the Braves ballpark. The Braves ballpark includes Truist Park. The Company’s segments include Baseball and Mixed-Use Development. The Baseball segment includes operations relating to Braves baseball and Truist Park and includes ticket sales, concessions, advertising sponsorships, suites and premium seat fees, broadcasting rights, retail and licensing. The Mixed-Use Development segment includes retail, office, hotel and entertainment operations primarily within The Battery Atlanta. The Battery Atlanta is an approximately 2.25 million square-foot mixed-use development, located around Truist Park at the intersection of I-75 and I-285, and offers an expansive mix of market-exclusive entertainment experiences, chef-driven restaurants, boutique shopping, the Omni and Aloft Hotels and others.</v>
     <v>1610</v>
@@ -6097,24 +6097,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>755 Battery Avenue Se, ATLANTA, GA, 30339 US</v>
-    <v>51.12</v>
+    <v>50.604999999999997</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46224.664017407034</v>
+    <v>46225.984182140623</v>
     <v>107</v>
-    <v>50.16</v>
-    <v>3230924213</v>
+    <v>49.7</v>
+    <v>3216812573</v>
     <v>ATLANTA BRAVES HOLDINGS, INC.</v>
     <v>ATLANTA BRAVES HOLDINGS, INC.</v>
-    <v>50.78</v>
+    <v>50.6</v>
     <v>0</v>
-    <v>51.23</v>
-    <v>50.37</v>
+    <v>50.29</v>
+    <v>50.15</v>
     <v>64143820</v>
     <v>BATRK</v>
     <v>ATLANTA BRAVES HOLDINGS, INC. (XNAS:BATRK)</v>
-    <v>161286</v>
-    <v>659853</v>
+    <v>467</v>
+    <v>659986</v>
     <v>2022</v>
   </rv>
   <rv s="2">
@@ -6138,9 +6138,9 @@
     <v>Powered by Refinitiv</v>
     <v>53.21</v>
     <v>30.51</v>
-    <v>1.7161</v>
-    <v>0.05</v>
-    <v>9.8390000000000001E-4</v>
+    <v>1.7191000000000001</v>
+    <v>0.81</v>
+    <v>1.5898000000000002E-2</v>
     <v>USD</v>
     <v>YETI Holdings, Inc. is a designer, retailer, and distributor of outdoor products. The Company's product portfolio consists of three categories: Coolers &amp; Equipment; Drinkware, and Other. Its Coolers &amp; Equipment family is comprised of hard coolers, soft coolers, cargo, bags, outdoor living, and associated accessories. Its hard cooler category includes YETI Tundra, YETI Roadie, YETI V Series hard coolers, YETI TANK ice, and YETI Silo 6G water cooler. The Hopper soft cooler product line includes Hopper M15 Soft Cooler, Hopper M12 Soft Backpack Cooler, Hopper M30 Soft Cooler, Hopper Flip Soft Cooler, and Daytrip Lunch Bag, among others. Its Drinkware product line consists of Rambler Colsters, Rambler Lowball, Rambler Wine Tumblers, Rambler Stackable Pints, Rambler Mugs, Rambler Tumblers, Rambler Straw Mugs and Cups, Rambler Bottles, Rambler Jugs, and Yonder Water Bottles. The Other category offers an array of apparel and gear, such as hats, shirts, bottle openers and ice substitutes.</v>
     <v>1390</v>
@@ -6148,24 +6148,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>7601 Southwest Pkwy, AUSTIN, TX, 78735-8989 US</v>
-    <v>51.024999999999999</v>
+    <v>52.06</v>
     <v>Leisure Products</v>
     <v>Stock</v>
-    <v>46224.664039142968</v>
+    <v>46225.982004200778</v>
     <v>110</v>
-    <v>49.58</v>
-    <v>3853825738</v>
+    <v>50.62</v>
+    <v>3921250643</v>
     <v>YETI HOLDINGS, INC.</v>
     <v>YETI HOLDINGS, INC.</v>
-    <v>50.875</v>
-    <v>25.772600000000001</v>
-    <v>50.82</v>
-    <v>50.87</v>
+    <v>51.5</v>
+    <v>26.2241</v>
+    <v>50.95</v>
+    <v>51.76</v>
     <v>75758320</v>
     <v>YETI</v>
     <v>YETI HOLDINGS, INC. (XNYS:YETI)</v>
-    <v>582010</v>
-    <v>1142749</v>
+    <v>66</v>
+    <v>1146556</v>
     <v>2012</v>
   </rv>
   <rv s="2">
@@ -6181,7 +6181,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a246z2</v>
     <v>268435456</v>
@@ -6189,9 +6189,9 @@
     <v>Powered by Refinitiv</v>
     <v>144.4</v>
     <v>83.44</v>
-    <v>0.9607</v>
-    <v>-0.35</v>
-    <v>-2.5069999999999997E-3</v>
+    <v>0.96779999999999999</v>
+    <v>-0.56000000000000005</v>
+    <v>-4.0439999999999999E-3</v>
     <v>USD</v>
     <v>Target Corporation is a general merchandise retailer selling products to its guests through its stores and digital channels. The Company offers customers, referred to as guests, differentiated merchandise and everyday essentials at discounted prices. The majority of its stores offer a wide assortment of general merchandise and groceries. Its merchandise categories include apparel and accessories, beauty, food and beverage, hardlines, home furnishings and decor, household essentials, and other merchandise sales. Most of its stores are larger than over 170,000 square feet, offer a variety of general merchandise and a full line of groceries comparable to traditional supermarkets. Its digital channels include merchandise assortment, including many items found in its stores, along with a complementary assortment sold by the Company and third parties through our Target Plus digital marketplace. Its brands include A New Day, All in Motion, Art Class, Auden, Ava &amp; Viv, among others.</v>
     <v>415000</v>
@@ -6199,24 +6199,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1000 Nicollet Mall, MINNEAPOLIS, MN, 55403 US</v>
-    <v>139.63</v>
+    <v>139.69</v>
     <v>Diversified Retail</v>
     <v>Stock</v>
-    <v>46224.664076654684</v>
+    <v>46225.993653078127</v>
     <v>113</v>
-    <v>137.67769999999999</v>
-    <v>63241568764</v>
+    <v>137.18</v>
+    <v>62642036511</v>
     <v>TARGET CORPORATION</v>
     <v>TARGET CORPORATION</v>
-    <v>138.86000000000001</v>
-    <v>17.125</v>
-    <v>139.59</v>
-    <v>139.24</v>
+    <v>139.22</v>
+    <v>16.962599999999998</v>
+    <v>138.47999999999999</v>
+    <v>137.91999999999999</v>
     <v>454191100</v>
     <v>TGT</v>
     <v>TARGET CORPORATION (XNYS:TGT)</v>
-    <v>668279</v>
-    <v>4775680</v>
+    <v>1071</v>
+    <v>4680087</v>
     <v>1902</v>
   </rv>
   <rv s="2">
@@ -6232,7 +6232,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1wljc</v>
     <v>268435456</v>
@@ -6240,9 +6240,9 @@
     <v>Powered by Refinitiv</v>
     <v>85.68</v>
     <v>65.353800000000007</v>
-    <v>0.34370000000000001</v>
-    <v>-8.5000000000000006E-2</v>
-    <v>-1.0349999999999999E-3</v>
+    <v>0.34439999999999998</v>
+    <v>0.23</v>
+    <v>2.8060000000000003E-3</v>
     <v>USD</v>
     <v>The Coca-Cola Company is a beverage company. The Company's segments include Europe, Middle East and Africa (EMEA); Latin America; North America; Asia Pacific, and Bottling Investments. It sells multiple brands across several beverage categories worldwide. Its portfolio of sparkling soft drink brands includes Coca-Cola, Sprite and Fanta. Its water, sports, coffee and tea brands include Dasani, smartwater, vitaminwater, Topo Chico, BODYARMOR, Powerade, Costa, Georgia, Fuze Tea, Gold Peak and Ayataka. Its juice, value-added dairy and plant-based beverage brands include Minute Maid, Simply, innocent, Del Valle, fairlife and Santa Clara. It operates in two lines of business: concentrate operations and finished product operations. Its concentrate operations sell beverage concentrates, syrups, including fountain syrups, and certain finished beverages to authorized bottling operations. Its finished product operations sell sparkling soft drinks and a variety of other finished beverages.</v>
     <v>65900</v>
@@ -6250,24 +6250,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1 Coca Cola Plz NW, ATLANTA, GA, 30313-2420 US</v>
-    <v>82.355000000000004</v>
+    <v>82.92</v>
     <v>Beverages</v>
     <v>Stock</v>
-    <v>46224.664082464842</v>
+    <v>46225.999999085157</v>
     <v>116</v>
-    <v>81.33</v>
-    <v>352954110870</v>
+    <v>81.954999999999998</v>
+    <v>353664020400</v>
     <v>THE COCA-COLA COMPANY</v>
     <v>THE COCA-COLA COMPANY</v>
-    <v>81.944999999999993</v>
-    <v>25.825600000000001</v>
-    <v>82.12</v>
-    <v>82.034999999999997</v>
+    <v>82.85</v>
+    <v>25.877800000000001</v>
+    <v>81.97</v>
+    <v>82.2</v>
     <v>4302482000</v>
     <v>KO</v>
     <v>THE COCA-COLA COMPANY (XNYS:KO)</v>
-    <v>4893827</v>
-    <v>20013554</v>
+    <v>60755</v>
+    <v>20061223</v>
     <v>1919</v>
   </rv>
   <rv s="2">
@@ -6281,9 +6281,9 @@
     <v>0</v>
     <v>Adidas AG (XFRA:ADS)</v>
     <v>2</v>
-    <v>16</v>
+    <v>19</v>
     <v>Finance</v>
-    <v>15</v>
+    <v>18</v>
     <v>en-US</v>
     <v>af3y27</v>
     <v>268435456</v>
@@ -6291,9 +6291,9 @@
     <v>Powered by Refinitiv</v>
     <v>335.05</v>
     <v>93.44</v>
-    <v>1.2045999999999999</v>
-    <v>-0.25</v>
-    <v>-1.3860000000000001E-3</v>
+    <v>1.2090000000000001</v>
+    <v>-1.3</v>
+    <v>-7.2589999999999998E-3</v>
     <v>EUR</v>
     <v>Adidas AG is a Germany-based company that designs, develops, produces, and markets a range of athletic and sports lifestyle products. The Company's segments include Europe, North America, Asia-Pacific, Russia/CIS, Latin America; Emerging Markets, Adidas Golf, Runtastic, and other centrally managed businesses. Its segment includes wholesale, retail, and e-commerce business activities relating to the distribution and sale of products of the Adidas brand to retail customers and end consumers. The Company has over 2,500 own-retail stores, mono-branded franchise stores, shop-in-shops, joint ventures with retail partners and co-branded stores, and an e-commerce channel, which is available to customers in over 50 countries. Adidas branded products include footwear, apparel, and hardware, such as bags and balls.</v>
     <v>64938</v>
@@ -6301,24 +6301,24 @@
     <v>XFRA</v>
     <v>XFRA</v>
     <v>Adi-Dassler-Strasse 1, HERZOGENAURACH, BAYERN, 91074 DE</v>
-    <v>180.85</v>
+    <v>178</v>
     <v>Textiles &amp; Apparel</v>
     <v>Stock</v>
-    <v>46224.652777777781</v>
+    <v>46226.504166666666</v>
     <v>119</v>
-    <v>178.95</v>
-    <v>32741750000</v>
+    <v>177.8</v>
+    <v>32265000000</v>
     <v>Adidas AG</v>
     <v>Adidas AG</v>
-    <v>180.85</v>
-    <v>23.3658</v>
-    <v>180.4</v>
-    <v>180.15</v>
+    <v>178</v>
+    <v>23.061</v>
+    <v>179.1</v>
+    <v>177.8</v>
     <v>180000000</v>
     <v>ADS</v>
     <v>Adidas AG (XFRA:ADS)</v>
-    <v>180</v>
-    <v>540090</v>
+    <v>40</v>
+    <v>520610</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -6334,17 +6334,17 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1pxbh</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>54.2</v>
+    <v>53.03</v>
     <v>28.035</v>
-    <v>0.94720000000000004</v>
-    <v>0.28499999999999998</v>
-    <v>8.6020000000000003E-3</v>
+    <v>0.94930000000000003</v>
+    <v>-1.1200000000000001</v>
+    <v>-3.3612999999999997E-2</v>
     <v>USD</v>
     <v>Chipotle Mexican Grill, Inc. is a restaurant company. The Company develops and operates restaurants that serve a menu of burritos, burrito bowls, quesadillas, tacos, and salads, made using fresh ingredients. The Company operates approximately 3839 restaurants in the United States, Canada, the United Kingdom, France, Germany, Kuwait, and United Arab Emirates. It owns and operates all its restaurants in North America and Europe. The Company is focused in serving sourced, classically cooked, real food with wholesome ingredients without artificial colors, flavors or preservatives. Its menu includes Burrito, Burrito Bowl, Lifestyle Bowl, Quesadilla, Salad, Tacos, Kid’s Meal, Chips and Sides, and Build your Own (digital only). It also includes Raymonte’s Chicken Bowl, The Mr. Fantasy Burrito, Carne Asada, Build-Your-Own Chipotle, catering and group order. Its subsidiaries include Chipotle Mexican Grill Canada Corp., Chipotle Mexican Grill France SAS, among others.</v>
     <v>130301</v>
@@ -6352,36 +6352,36 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>610 Newport Center Dr., NEWPORT BEACH, CA, 92660 US</v>
-    <v>33.619999999999997</v>
+    <v>33.369999999999997</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46224.664044467187</v>
+    <v>46225.999965625</v>
     <v>122</v>
-    <v>32.21</v>
-    <v>42862556610</v>
+    <v>31.8825</v>
+    <v>41304034800</v>
     <v>CHIPOTLE MEXICAN GRILL, INC.</v>
     <v>CHIPOTLE MEXICAN GRILL, INC.</v>
-    <v>32.520000000000003</v>
-    <v>30.5886</v>
-    <v>33.130000000000003</v>
-    <v>33.414999999999999</v>
+    <v>33.369999999999997</v>
+    <v>29.477499999999999</v>
+    <v>33.32</v>
+    <v>32.200000000000003</v>
     <v>1282734000</v>
     <v>CMG</v>
     <v>CHIPOTLE MEXICAN GRILL, INC. (XNYS:CMG)</v>
-    <v>4195570</v>
-    <v>19631817</v>
+    <v>5258</v>
+    <v>19264833</v>
     <v>1998</v>
   </rv>
   <rv s="2">
     <v>123</v>
   </rv>
-  <rv s="8">
-    <v>17</v>
+  <rv s="9">
+    <v>20</v>
     <v>Amer Sports, Inc (XNYS:AS)</v>
-    <v>18</v>
+    <v>21</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>ccac9c</v>
     <v>268435456</v>
@@ -6389,9 +6389,9 @@
     <v>Powered by Refinitiv</v>
     <v>42.76</v>
     <v>28.92</v>
-    <v>0.73499999999999999</v>
-    <v>-1.66</v>
-    <v>-4.5679999999999998E-2</v>
+    <v>0.70899999999999996</v>
+    <v>-0.12</v>
+    <v>-3.4780000000000002E-3</v>
     <v>USD</v>
     <v>Amer Sports Inc is a Finland-based global group of sports and outdoor brands such as Arcteryx, Salomon, Wilson, Peak Performance, Atomic, Armada, ATEC, DeMarini, EvoShield and ENVE. The Company develops, manufactures, and markets sports and fitness equipment. Its products include sports equipment for tennis, badminton, soccer, baseball, basketball, golf, American football, alpine skiing, fitness training, cycling, running, hiking, snowboarding, cross-country skiing and diving. It also offers fitness equipment through factory outlets, and e-commerce companies through trade customers in sporting goods chains, mass merchants, specialty retailers, fitness clubs, and distributors. The Company operates worldwide.</v>
     <v>15400</v>
@@ -6399,23 +6399,23 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>Siltasaarenkatu 8-10, Fl-00530, HELSINKI, ETELA-SUOMEN, 00511 FI</v>
-    <v>36.380000000000003</v>
+    <v>34.71</v>
     <v>Specialty Retailers</v>
     <v>Stock</v>
-    <v>46224.664079513284</v>
-    <v>34.24</v>
-    <v>20054466024</v>
+    <v>46225.982069316407</v>
+    <v>33.405000000000001</v>
+    <v>19880984484</v>
     <v>Amer Sports, Inc</v>
     <v>Amer Sports, Inc</v>
-    <v>36.174999999999997</v>
-    <v>42.973999999999997</v>
-    <v>36.340000000000003</v>
-    <v>34.68</v>
+    <v>34.299999999999997</v>
+    <v>42.604300000000002</v>
+    <v>34.5</v>
+    <v>34.380000000000003</v>
     <v>578271800</v>
     <v>AS</v>
     <v>Amer Sports, Inc (XNYS:AS)</v>
-    <v>2536466</v>
-    <v>3601390</v>
+    <v>51</v>
+    <v>3899880</v>
     <v>2020</v>
   </rv>
   <rv s="2">
@@ -6431,7 +6431,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1yjxm</v>
     <v>268435456</v>
@@ -6439,9 +6439,9 @@
     <v>Powered by Refinitiv</v>
     <v>80.165000000000006</v>
     <v>40</v>
-    <v>1.1054999999999999</v>
-    <v>-0.33</v>
-    <v>-7.5909999999999997E-3</v>
+    <v>1.1144000000000001</v>
+    <v>-0.75</v>
+    <v>-1.7458000000000001E-2</v>
     <v>USD</v>
     <v>NIKE, Inc. is engaged in the designing, marketing and distributing of athletic footwear, apparel, equipment and accessories and services for sports and fitness activities. The Company's operating segments include North America; Europe, Middle East &amp; Africa (EMEA); Greater China; and Asia Pacific &amp; Latin America (APLA). It sells a line of equipment and accessories under the NIKE Brand name, including bags, socks, sport balls, eyewear, timepieces, digital devices, bats, gloves, protective equipment and other equipment designed for sports activities. It also designs products specifically for the Jordan Brand and Converse. The Jordan Brand designs, distributes and licenses athletic and casual footwear, apparel and accessories predominantly focused on basketball performance and culture using the Jumpman trademark. The Company also designs, distributes and licenses casual sneakers, apparel and accessories under the Chuck Taylor, All Star, One Star, Star Chevron and Jack Purcell trademarks.</v>
     <v>73000</v>
@@ -6449,24 +6449,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Bowerman Dr, BEAVERTON, OR, 97005-6453 US</v>
-    <v>43.56</v>
+    <v>42.91</v>
     <v>Textiles &amp; Apparel</v>
     <v>Stock</v>
-    <v>46224.664066712503</v>
+    <v>46225.999707233597</v>
     <v>127</v>
-    <v>42.75</v>
-    <v>63998146860</v>
+    <v>41.57</v>
+    <v>62618492790</v>
     <v>NIKE, INC.</v>
     <v>NIKE, INC.</v>
-    <v>43.1</v>
-    <v>20.560500000000001</v>
-    <v>43.47</v>
-    <v>43.14</v>
+    <v>42.45</v>
+    <v>20.117100000000001</v>
+    <v>42.96</v>
+    <v>42.21</v>
     <v>1483499000</v>
     <v>NKE</v>
     <v>NIKE, INC. (XNYS:NKE)</v>
-    <v>4180551</v>
-    <v>26538510</v>
+    <v>60969</v>
+    <v>26351900</v>
     <v>1969</v>
   </rv>
   <rv s="2">
@@ -6480,9 +6480,9 @@
     <v>0</v>
     <v>Logitech international SA (XNAS:LOGI)</v>
     <v>2</v>
-    <v>19</v>
+    <v>22</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1x252</v>
     <v>268435456</v>
@@ -6490,9 +6490,9 @@
     <v>Powered by Refinitiv</v>
     <v>129.66</v>
     <v>83.32</v>
-    <v>0.94920000000000004</v>
-    <v>2.645</v>
-    <v>2.5987E-2</v>
+    <v>0.94789999999999996</v>
+    <v>1.51</v>
+    <v>1.4673E-2</v>
     <v>USD</v>
     <v>Logitech International SA is a Switzerland-based holding company. The Company’s purpose is to coordinate the activities of the various Swiss and foreign subsidiaries of the Logitech group. The Company focuses on designing and manufacturing products that enable people to connect and interact with digital content. Its portfolio includes Gaming, Keyboards &amp; Combos, Pointing Devices, Video Collaboration, Webcams, Tablet Accessories, and Headsets. The Company sells its products to a broad range of international customers, in the Americas, Europe, the Middle East, Africa and Asia Pacific. This includes direct sales to retailers, e-tailers, businesses large and small and end consumers through our e-commerce platform, and indirect sales to end customers through distributors.</v>
     <v>7300</v>
@@ -6500,24 +6500,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>Route de Pampigny 20, APPLES, VAUD, 1143 CH</v>
-    <v>104.8</v>
+    <v>105.66</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46224.66402278906</v>
+    <v>46225.982075300781</v>
     <v>130</v>
-    <v>103.38</v>
-    <v>13323570000</v>
+    <v>104.01</v>
+    <v>13748370000</v>
     <v>Logitech international SA</v>
     <v>Logitech international SA</v>
-    <v>103.58</v>
-    <v>21.768799999999999</v>
-    <v>101.78</v>
-    <v>104.425</v>
+    <v>104.04</v>
+    <v>21.767700000000001</v>
+    <v>102.91</v>
+    <v>104.42</v>
     <v>160784500</v>
     <v>LOGI</v>
     <v>Logitech international SA (XNAS:LOGI)</v>
-    <v>357437</v>
-    <v>990525</v>
+    <v>4727</v>
+    <v>1001520</v>
     <v>1988</v>
   </rv>
   <rv s="2">
@@ -6533,7 +6533,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1zsjc</v>
     <v>268435456</v>
@@ -6541,9 +6541,9 @@
     <v>Powered by Refinitiv</v>
     <v>167.25</v>
     <v>137.62</v>
-    <v>0.37219999999999998</v>
-    <v>-1.615</v>
-    <v>-1.0829E-2</v>
+    <v>0.37369999999999998</v>
+    <v>1.03</v>
+    <v>6.9550000000000002E-3</v>
     <v>USD</v>
     <v>The Procter &amp; Gamble Company is focused on providing branded consumer packaged goods to consumers across the world. The Company’s segments include Beauty, Grooming, Health Care, Fabric &amp; Home Care and Baby, Feminine &amp; Family Care. The Company’s products are sold in approximately 180 countries and territories primarily through mass merchandisers, e-commerce, including social commerce channels, grocery stores, membership club stores, drug stores, department stores, distributors, wholesalers, specialty beauty stores, including airport duty-free stores), high-frequency stores, pharmacies, electronics stores and professional channels. It also sells direct to individual consumers. It has operations in approximately 70 countries. It offers products under brands, such as Head &amp; Shoulders, Herbal Essences, Pantene, Rejoice, Olay, Old Spice, Safeguard, Secret, SK-II, Braun, Gillette, Venus, Crest, Oral-B, Ariel, Downy, Gain, Tide, Always, Always Discreet, Tampax, Bounty and others.</v>
     <v>109000</v>
@@ -6551,24 +6551,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Procter &amp; Gamble Plaza, CINCINNATI, OH, 45202 US</v>
-    <v>148.285</v>
+    <v>150.46</v>
     <v>Personal &amp; Household Products &amp; Services</v>
     <v>Stock</v>
-    <v>46224.664079628907</v>
+    <v>46225.995739490623</v>
     <v>133</v>
-    <v>146.88</v>
-    <v>343503281484</v>
+    <v>148.815</v>
+    <v>347263968870</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY</v>
-    <v>148.28</v>
-    <v>21.574100000000001</v>
+    <v>149.5</v>
+    <v>21.810300000000002</v>
+    <v>148.1</v>
     <v>149.13</v>
-    <v>147.51499999999999</v>
     <v>2328599000</v>
     <v>PG</v>
     <v>THE PROCTER &amp; GAMBLE COMPANY (XNYS:PG)</v>
-    <v>1609363</v>
-    <v>9411309</v>
+    <v>30313</v>
+    <v>9419132</v>
     <v>1905</v>
   </rv>
   <rv s="2">
@@ -6584,7 +6584,7 @@
     <v>2</v>
     <v>3</v>
     <v>Finance</v>
-    <v>4</v>
+    <v>5</v>
     <v>en-US</v>
     <v>a1plbh</v>
     <v>268435456</v>
@@ -6592,9 +6592,9 @@
     <v>Powered by Refinitiv</v>
     <v>118.455</v>
     <v>80.239999999999995</v>
-    <v>0.68500000000000005</v>
-    <v>7.0000000000000007E-2</v>
-    <v>8.3620000000000005E-4</v>
+    <v>0.68340000000000001</v>
+    <v>-1.19</v>
+    <v>-1.4280999999999999E-2</v>
     <v>USD</v>
     <v>Churchill Downs Incorporated is a racing, online wagering and gaming entertainment company, which is anchored by its flagship event, the Kentucky Derby. The Company operates through three reportable segments: Live and Historical Racing, Wagering Services and Solutions, and Gaming. The Live and Historical Racing segment includes live and historical pari-mutuel racing at Churchill Downs Racetrack and its historical racing properties in Kentucky, Virginia and New Hampshire. The Wagering Services and Solutions segment includes TwinSpires, which is a retail and online sports betting business; United Tote Company, which manufactures and operates pari-mutuel wagering systems for racetracks, off-track betting facilities (OTBs), and other pari-mutuel wagering businesses; and Exacta Systems, LLC that provides central determinant system technology in historical racing machine (HRMs) across the country. The Gaming segment is engaged in the casino properties and associated racetrack facilities.</v>
     <v>6600</v>
@@ -6602,24 +6602,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>600 N. Hurstbourne Parkway, Suite 400, LOUISVILLE, KY, 40222 US</v>
-    <v>84.27</v>
+    <v>83.56</v>
     <v>Hotels &amp; Entertainment Services</v>
     <v>Stock</v>
-    <v>46224.664042626566</v>
+    <v>46225.98207210625</v>
     <v>136</v>
-    <v>82.770099999999999</v>
-    <v>5839207119</v>
+    <v>81.95</v>
+    <v>5724904187</v>
     <v>CHURCHILL DOWNS INCORPORATED</v>
     <v>CHURCHILL DOWNS INCORPORATED</v>
-    <v>83.59</v>
-    <v>15.520899999999999</v>
-    <v>83.71</v>
-    <v>83.78</v>
+    <v>83.33</v>
+    <v>15.2171</v>
+    <v>83.33</v>
+    <v>82.14</v>
     <v>69696910</v>
     <v>CHDN</v>
     <v>CHURCHILL DOWNS INCORPORATED (XNAS:CHDN)</v>
-    <v>141983</v>
-    <v>1059514</v>
+    <v>452</v>
+    <v>1054347</v>
     <v>1937</v>
   </rv>
   <rv s="2">
@@ -6644,8 +6644,8 @@
     <v>119.65</v>
     <v>73.09</v>
     <v>0.81289999999999996</v>
-    <v>-1.0900000000000001</v>
-    <v>-9.7729999999999987E-3</v>
+    <v>-2.7</v>
+    <v>-2.4680000000000001E-2</v>
     <v>USD</v>
     <v>Acushnet Holdings Corp. is engaged in the design, development, manufacture and distribution of performance-driven golf products. The Company’s segments include Titleist golf equipment, FootJoy golf wear, and Golf gear. The Titleist golf equipment segment includes Titleist and Pinnacle branded golf balls; PG Golf recycled golf balls; Titleist branded golf clubs, including drivers, fairways, hybrids and irons; Vokey Design wedges; Scotty Cameron putters and Titleist Performance Institute. The FootJoy golf wear segment includes FootJoy branded golf shoes, golf gloves, golf outerwear and golf apparel. The Golf gear segment includes Titleist branded golf bags, headwear, golf gloves, travel gear and other golf accessories, as well as Club Glove travel products and Links &amp; Kings luxury leather golf goods. It designs, manufactures and markets a range of products under the Titleist, FootJoy, KJUS, and other brands.</v>
     <v>7300</v>
@@ -6653,24 +6653,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>333 Bridge St, FAIRHAVEN, MA, 02719-4905 US</v>
-    <v>112.85</v>
+    <v>109.57</v>
     <v>Leisure Products</v>
     <v>Stock</v>
-    <v>46224.66395929375</v>
+    <v>46225.982030034378</v>
     <v>139</v>
-    <v>110.07</v>
-    <v>6466709282</v>
+    <v>106.27</v>
+    <v>6247717135</v>
     <v>ACUSHNET HOLDINGS CORP.</v>
     <v>ACUSHNET HOLDINGS CORP.</v>
-    <v>112.84</v>
-    <v>38.991700000000002</v>
-    <v>111.53</v>
-    <v>110.44</v>
+    <v>108.53</v>
+    <v>37.671100000000003</v>
+    <v>109.4</v>
+    <v>106.7</v>
     <v>58554050</v>
     <v>GOLF</v>
     <v>ACUSHNET HOLDINGS CORP. (XNYS:GOLF)</v>
-    <v>40052</v>
-    <v>376739</v>
+    <v>238992</v>
+    <v>370572</v>
     <v>2011</v>
   </rv>
   <rv s="2">
@@ -6680,7 +6680,7 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -6731,6 +6731,49 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change (%)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
   </s>
   <s t="_sourceattribution">
     <k n="License" t="r"/>
@@ -6870,7 +6913,7 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="4">
+  <spbArrays count="5">
     <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
@@ -6901,6 +6944,49 @@
       <v t="s">Market cap</v>
       <v t="s">Beta</v>
       <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
+    <a count="41">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
       <v t="s">Shares outstanding</v>
       <v t="s">Description</v>
       <v t="s">Employees</v>
@@ -7032,7 +7118,7 @@
       <v t="s">%ProviderInfo</v>
     </a>
   </spbArrays>
-  <spbData count="20">
+  <spbData count="23">
     <spb s="0">
       <v>0</v>
       <v>Name</v>
@@ -7072,6 +7158,13 @@
       <v>4</v>
     </spb>
     <spb s="4">
+      <v>Delayed 15 minutes</v>
+      <v>from previous close</v>
+      <v>from previous close</v>
+      <v>Source: Nasdaq</v>
+      <v>GMT</v>
+    </spb>
+    <spb s="4">
       <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
@@ -7084,17 +7177,43 @@
       <v>LearnMoreOnLink</v>
     </spb>
     <spb s="5">
+      <v>1</v>
+      <v>2</v>
+      <v>1</v>
+      <v>3</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>4</v>
+      <v>5</v>
+      <v>6</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>7</v>
+      <v>8</v>
+      <v>9</v>
+      <v>4</v>
+    </spb>
+    <spb s="0">
+      <v>2</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
+    <spb s="6">
       <v>0</v>
       <v>0</v>
     </spb>
-    <spb s="6">
-      <v>6</v>
+    <spb s="7">
+      <v>9</v>
       <v>1</v>
       <v>1</v>
       <v>1</v>
       <v>1</v>
     </spb>
-    <spb s="7">
+    <spb s="8">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -7117,20 +7236,20 @@
       <v>9</v>
       <v>4</v>
     </spb>
-    <spb s="8">
+    <spb s="9">
       <v>Powered by Refinitiv</v>
     </spb>
     <spb s="0">
-      <v>2</v>
+      <v>3</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="9">
+    <spb s="10">
       <v>1</v>
       <v>1</v>
       <v>1</v>
     </spb>
-    <spb s="10">
+    <spb s="11">
       <v>1</v>
       <v>1</v>
       <v>3</v>
@@ -7143,7 +7262,7 @@
       <v>1</v>
       <v>9</v>
     </spb>
-    <spb s="11">
+    <spb s="12">
       <v>from previous close</v>
       <v>from previous close</v>
     </spb>
@@ -7169,7 +7288,7 @@
       <v>9</v>
       <v>4</v>
     </spb>
-    <spb s="12">
+    <spb s="13">
       <v>Delayed 15 minutes</v>
       <v>from previous close</v>
       <v>from previous close</v>
@@ -7197,11 +7316,11 @@
       <v>9</v>
       <v>4</v>
     </spb>
-    <spb s="13">
-      <v>3</v>
+    <spb s="14">
+      <v>4</v>
       <v>Name</v>
     </spb>
-    <spb s="14">
+    <spb s="15">
       <v>1</v>
       <v>1</v>
       <v>1</v>
@@ -7233,7 +7352,7 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="15">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="16">
   <s>
     <k n="^Order" t="spba"/>
     <k n="TitleProperty" t="s"/>
@@ -7278,6 +7397,27 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+  </s>
+  <s>
+    <k n="Low" t="i"/>
+    <k n="Beta" t="i"/>
+    <k n="High" t="i"/>
+    <k n="Name" t="i"/>
+    <k n="Open" t="i"/>
+    <k n="Price" t="i"/>
+    <k n="Change" t="i"/>
+    <k n="Volume" t="i"/>
+    <k n="Employees" t="i"/>
+    <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
+    <k n="52 week low" t="i"/>
+    <k n="52 week high" t="i"/>
+    <k n="Previous close" t="i"/>
+    <k n="Volume average" t="i"/>
+    <k n="Last trade time" t="i"/>
+    <k n="Year incorporated" t="i"/>
+    <k n="`%EntityServiceId" t="i"/>
+    <k n="Shares outstanding" t="i"/>
   </s>
   <s>
     <k n="ShowInDotNotation" t="b"/>
@@ -7764,6 +7904,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions val="1"/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>FDS</we:customFunctionIds>
@@ -9199,51 +9342,51 @@
         <v>92</v>
       </c>
       <c r="N12" s="17">
-        <f t="shared" ref="N12:Q12" si="1">SUM(N4:N11)</f>
+        <f>SUM(N4:N11)</f>
         <v>85</v>
       </c>
       <c r="O12" s="17">
-        <f t="shared" si="1"/>
+        <f>SUM(O4:O11)</f>
         <v>94</v>
       </c>
       <c r="P12" s="17">
+        <f>SUM(P4:P11)</f>
+        <v>92</v>
+      </c>
+      <c r="Q12" s="17">
+        <f>SUM(Q4:Q11)</f>
+        <v>80</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" ref="R12:Y12" si="1">SUM(R4:R11)</f>
+        <v>75</v>
+      </c>
+      <c r="S12" s="17">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="Q12" s="17">
+      <c r="T12" s="17">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="R12" s="17">
-        <f t="shared" ref="R12:Y12" si="2">SUM(R4:R11)</f>
+        <v>90</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="S12" s="17">
-        <f t="shared" si="2"/>
-        <v>92</v>
-      </c>
-      <c r="T12" s="17">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="2"/>
-        <v>92</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="2"/>
-        <v>85</v>
-      </c>
-      <c r="W12">
-        <f t="shared" si="2"/>
-        <v>96</v>
-      </c>
-      <c r="X12">
-        <f t="shared" si="2"/>
-        <v>75</v>
-      </c>
       <c r="Y12" s="145">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>97</v>
       </c>
     </row>
@@ -10693,7 +10836,7 @@
         <v>170</v>
       </c>
       <c r="C10" s="152">
-        <f t="shared" ref="C10" si="0">C9+2</f>
+        <f>C9+2</f>
         <v>46065</v>
       </c>
       <c r="D10" s="152"/>
@@ -10713,7 +10856,7 @@
         <v>171</v>
       </c>
       <c r="C11" s="152">
-        <f t="shared" ref="C11" si="1">C9+7</f>
+        <f>C9+7</f>
         <v>46070</v>
       </c>
       <c r="D11" s="152" t="s">
@@ -10737,7 +10880,7 @@
         <v>170</v>
       </c>
       <c r="C12" s="152">
-        <f t="shared" ref="C12" si="2">C11+2</f>
+        <f>C11+2</f>
         <v>46072</v>
       </c>
       <c r="D12" s="152"/>
@@ -10760,7 +10903,7 @@
         <v>171</v>
       </c>
       <c r="C13" s="152">
-        <f t="shared" ref="C13" si="3">C11+7</f>
+        <f>C11+7</f>
         <v>46077</v>
       </c>
       <c r="G13" s="70" t="s">
@@ -10775,7 +10918,7 @@
         <v>170</v>
       </c>
       <c r="C14" s="152">
-        <f t="shared" ref="C14" si="4">C13+2</f>
+        <f>C13+2</f>
         <v>46079</v>
       </c>
       <c r="D14" s="152" t="s">
@@ -10803,7 +10946,7 @@
         <v>171</v>
       </c>
       <c r="C15" s="152">
-        <f t="shared" ref="C15" si="5">C13+7</f>
+        <f>C13+7</f>
         <v>46084</v>
       </c>
       <c r="D15" s="152"/>
@@ -10873,7 +11016,7 @@
         <v>170</v>
       </c>
       <c r="C18" s="152">
-        <f t="shared" ref="C18" si="6">C17+2</f>
+        <f>C17+2</f>
         <v>46093</v>
       </c>
       <c r="D18" s="152"/>
@@ -10893,7 +11036,7 @@
         <v>171</v>
       </c>
       <c r="C19" s="152">
-        <f t="shared" ref="C19" si="7">C17+7</f>
+        <f>C17+7</f>
         <v>46098</v>
       </c>
       <c r="E19" s="203" t="s">
@@ -10906,7 +11049,7 @@
         <v>170</v>
       </c>
       <c r="C20" s="152">
-        <f t="shared" ref="C20" si="8">C19+2</f>
+        <f>C19+2</f>
         <v>46100</v>
       </c>
       <c r="D20" s="160"/>
@@ -10923,7 +11066,7 @@
         <v>171</v>
       </c>
       <c r="C21" s="160">
-        <f t="shared" ref="C21" si="9">C19+7</f>
+        <f>C19+7</f>
         <v>46105</v>
       </c>
       <c r="D21" s="152"/>
@@ -10937,7 +11080,7 @@
         <v>170</v>
       </c>
       <c r="C22" s="160">
-        <f t="shared" ref="C22" si="10">C21+2</f>
+        <f>C21+2</f>
         <v>46107</v>
       </c>
       <c r="D22" s="152"/>
@@ -10957,7 +11100,7 @@
         <v>171</v>
       </c>
       <c r="C23" s="152">
-        <f t="shared" ref="C23:C31" si="11">C21+7</f>
+        <f t="shared" ref="C23:C31" si="0">C21+7</f>
         <v>46112</v>
       </c>
       <c r="D23" s="152"/>
@@ -10979,7 +11122,7 @@
         <v>170</v>
       </c>
       <c r="C24" s="152">
-        <f t="shared" ref="C24:C32" si="12">C23+2</f>
+        <f t="shared" ref="C24:C32" si="1">C23+2</f>
         <v>46114</v>
       </c>
       <c r="D24" s="152"/>
@@ -10999,7 +11142,7 @@
         <v>171</v>
       </c>
       <c r="C25" s="152">
-        <f t="shared" si="11"/>
+        <f t="shared" si="0"/>
         <v>46119</v>
       </c>
       <c r="D25" s="151"/>
@@ -11021,7 +11164,7 @@
         <v>170</v>
       </c>
       <c r="C26" s="152">
-        <f t="shared" si="12"/>
+        <f t="shared" si="1"/>
         <v>46121</v>
       </c>
       <c r="D26" s="158"/>
@@ -11045,7 +11188,7 @@
         <v>171</v>
       </c>
       <c r="C27" s="152">
-        <f t="shared" si="11"/>
+        <f t="shared" si="0"/>
         <v>46126</v>
       </c>
       <c r="D27" s="158" t="s">
@@ -11068,7 +11211,7 @@
         <v>170</v>
       </c>
       <c r="C28" s="152">
-        <f t="shared" si="12"/>
+        <f t="shared" si="1"/>
         <v>46128</v>
       </c>
       <c r="D28" s="151" t="s">
@@ -11095,7 +11238,7 @@
         <v>171</v>
       </c>
       <c r="C29" s="152">
-        <f t="shared" si="11"/>
+        <f t="shared" si="0"/>
         <v>46133</v>
       </c>
       <c r="D29" s="151" t="s">
@@ -11120,7 +11263,7 @@
         <v>170</v>
       </c>
       <c r="C30" s="152">
-        <f t="shared" si="12"/>
+        <f t="shared" si="1"/>
         <v>46135</v>
       </c>
       <c r="D30" s="151" t="s">
@@ -11147,7 +11290,7 @@
         <v>171</v>
       </c>
       <c r="C31" s="152">
-        <f t="shared" si="11"/>
+        <f t="shared" si="0"/>
         <v>46140</v>
       </c>
       <c r="D31" s="151" t="s">
@@ -11172,7 +11315,7 @@
         <v>170</v>
       </c>
       <c r="C32" s="152">
-        <f t="shared" si="12"/>
+        <f t="shared" si="1"/>
         <v>46142</v>
       </c>
       <c r="D32" s="151" t="s">
@@ -13581,7 +13724,7 @@
         <v>#Calc</v>
       </c>
       <c r="G30" s="112" t="e">
-        <f t="shared" ref="G30" ca="1" si="3">F30-E30</f>
+        <f ca="1">F30-E30</f>
         <v>#VALUE!</v>
       </c>
       <c r="H30" s="112"/>
@@ -13615,7 +13758,7 @@
       </c>
       <c r="P30" s="181"/>
       <c r="Q30" s="182" t="e">
-        <f t="shared" ref="Q30" ca="1" si="4">(F30-E30)/E30</f>
+        <f ca="1">(F30-E30)/E30</f>
         <v>#VALUE!</v>
       </c>
       <c r="R30" s="126" t="e">
@@ -13643,7 +13786,7 @@
         <v>6927.82</v>
       </c>
       <c r="G31" s="193">
-        <f t="shared" ref="G31:G32" si="5">F31-E31</f>
+        <f>F31-E31</f>
         <v>52.199999999999818</v>
       </c>
       <c r="H31" s="104"/>
@@ -13656,7 +13799,7 @@
       <c r="O31" s="106"/>
       <c r="P31" s="123"/>
       <c r="Q31" s="167">
-        <f t="shared" ref="Q31:Q32" si="6">(F31-E31)/E31</f>
+        <f>(F31-E31)/E31</f>
         <v>7.5920426085210957E-3</v>
       </c>
       <c r="R31" s="126" t="e">
@@ -13681,7 +13824,7 @@
         <v>#Calc</v>
       </c>
       <c r="G32" s="104" t="e">
-        <f t="shared" ca="1" si="5"/>
+        <f ca="1">F32-E32</f>
         <v>#VALUE!</v>
       </c>
       <c r="H32" s="104"/>
@@ -13715,7 +13858,7 @@
       </c>
       <c r="P32" s="123"/>
       <c r="Q32" s="167" t="e">
-        <f t="shared" ca="1" si="6"/>
+        <f ca="1">(F32-E32)/E32</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -16092,20 +16235,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="220" t="s">
+      <c r="A1" s="205" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="220" t="s">
+      <c r="B1" s="205" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="220" t="s">
+      <c r="C1" s="205" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="221"/>
-      <c r="B2" s="221"/>
-      <c r="C2" s="221"/>
+      <c r="A2" s="206"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="206"/>
     </row>
     <row r="3" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
@@ -16148,7 +16291,7 @@
       <c r="B7" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="209" t="s">
+      <c r="C7" s="207" t="s">
         <v>126</v>
       </c>
     </row>
@@ -16157,49 +16300,49 @@
       <c r="B8" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="215"/>
+      <c r="C8" s="208"/>
     </row>
     <row r="9" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
         <v>125</v>
       </c>
       <c r="B9" s="27"/>
-      <c r="C9" s="210"/>
+      <c r="C9" s="209"/>
     </row>
     <row r="10" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="31"/>
     </row>
     <row r="11" spans="1:4" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="216" t="s">
+      <c r="A11" s="210" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="216" t="s">
+      <c r="B11" s="210" t="s">
         <v>112</v>
       </c>
-      <c r="C11" s="216" t="s">
+      <c r="C11" s="210" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="216" t="s">
+      <c r="D11" s="210" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="217"/>
-      <c r="B12" s="217"/>
-      <c r="C12" s="217"/>
-      <c r="D12" s="217"/>
+      <c r="A12" s="211"/>
+      <c r="B12" s="211"/>
+      <c r="C12" s="211"/>
+      <c r="D12" s="211"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="205" t="s">
+      <c r="A13" s="212" t="s">
         <v>78</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="205" t="s">
+      <c r="C13" s="212" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="209">
+      <c r="D13" s="207">
         <v>15</v>
       </c>
     </row>
@@ -16209,81 +16352,81 @@
         <v>93</v>
       </c>
       <c r="C14" s="213"/>
-      <c r="D14" s="215"/>
+      <c r="D14" s="208"/>
     </row>
     <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="206"/>
+      <c r="A15" s="214"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="210"/>
+      <c r="C15" s="214"/>
+      <c r="D15" s="209"/>
     </row>
     <row r="16" spans="1:4" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="209"/>
-      <c r="B16" s="205" t="s">
+      <c r="A16" s="207"/>
+      <c r="B16" s="212" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="205" t="s">
+      <c r="C16" s="212" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="209"/>
+      <c r="D16" s="207"/>
     </row>
     <row r="17" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="210"/>
-      <c r="B17" s="206"/>
-      <c r="C17" s="206"/>
-      <c r="D17" s="210"/>
+      <c r="A17" s="209"/>
+      <c r="B17" s="214"/>
+      <c r="C17" s="214"/>
+      <c r="D17" s="209"/>
     </row>
     <row r="18" spans="1:4" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="209"/>
-      <c r="B18" s="205" t="s">
+      <c r="A18" s="207"/>
+      <c r="B18" s="212" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="205" t="s">
+      <c r="C18" s="212" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="211"/>
+      <c r="D18" s="215"/>
     </row>
     <row r="19" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="210"/>
-      <c r="B19" s="206"/>
-      <c r="C19" s="206"/>
-      <c r="D19" s="212"/>
+      <c r="A19" s="209"/>
+      <c r="B19" s="214"/>
+      <c r="C19" s="214"/>
+      <c r="D19" s="216"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="209"/>
+      <c r="A20" s="207"/>
       <c r="B20" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="205" t="s">
+      <c r="C20" s="212" t="s">
         <v>129</v>
       </c>
-      <c r="D20" s="211"/>
+      <c r="D20" s="215"/>
     </row>
     <row r="21" spans="1:4" ht="42" x14ac:dyDescent="0.2">
-      <c r="A21" s="215"/>
+      <c r="A21" s="208"/>
       <c r="B21" s="26" t="s">
         <v>128</v>
       </c>
       <c r="C21" s="213"/>
-      <c r="D21" s="214"/>
+      <c r="D21" s="217"/>
     </row>
     <row r="22" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="210"/>
+      <c r="A22" s="209"/>
       <c r="B22" s="32"/>
-      <c r="C22" s="206"/>
-      <c r="D22" s="212"/>
+      <c r="C22" s="214"/>
+      <c r="D22" s="216"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="205" t="s">
+      <c r="A23" s="212" t="s">
         <v>110</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="205" t="s">
+      <c r="C23" s="212" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="211">
+      <c r="D23" s="215">
         <v>10</v>
       </c>
     </row>
@@ -16291,7 +16434,7 @@
       <c r="A24" s="213"/>
       <c r="B24" s="26"/>
       <c r="C24" s="213"/>
-      <c r="D24" s="214"/>
+      <c r="D24" s="217"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="213"/>
@@ -16299,51 +16442,51 @@
         <v>131</v>
       </c>
       <c r="C25" s="213"/>
-      <c r="D25" s="214"/>
+      <c r="D25" s="217"/>
     </row>
     <row r="26" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="206"/>
+      <c r="A26" s="214"/>
       <c r="B26" s="32"/>
-      <c r="C26" s="206"/>
-      <c r="D26" s="212"/>
+      <c r="C26" s="214"/>
+      <c r="D26" s="216"/>
     </row>
     <row r="27" spans="1:4" ht="42" x14ac:dyDescent="0.2">
-      <c r="A27" s="209"/>
-      <c r="B27" s="205" t="s">
+      <c r="A27" s="207"/>
+      <c r="B27" s="212" t="s">
         <v>80</v>
       </c>
       <c r="C27" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="211"/>
+      <c r="D27" s="215"/>
     </row>
     <row r="28" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A28" s="215"/>
+      <c r="A28" s="208"/>
       <c r="B28" s="213"/>
       <c r="C28" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="214"/>
+      <c r="D28" s="217"/>
     </row>
     <row r="29" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A29" s="215"/>
+      <c r="A29" s="208"/>
       <c r="B29" s="213"/>
       <c r="C29" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="214"/>
+      <c r="D29" s="217"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="215"/>
+      <c r="A30" s="208"/>
       <c r="B30" s="213"/>
       <c r="C30" s="26"/>
-      <c r="D30" s="214"/>
+      <c r="D30" s="217"/>
     </row>
     <row r="31" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="210"/>
-      <c r="B31" s="206"/>
+      <c r="A31" s="209"/>
+      <c r="B31" s="214"/>
       <c r="C31" s="27"/>
-      <c r="D31" s="212"/>
+      <c r="D31" s="216"/>
     </row>
     <row r="32" spans="1:4" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33"/>
@@ -16352,13 +16495,13 @@
       <c r="D32" s="35"/>
     </row>
     <row r="33" spans="1:4" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="216" t="s">
+      <c r="A33" s="210" t="s">
         <v>120</v>
       </c>
-      <c r="B33" s="216" t="s">
+      <c r="B33" s="210" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="216" t="s">
+      <c r="C33" s="210" t="s">
         <v>77</v>
       </c>
       <c r="D33" s="218" t="s">
@@ -16366,22 +16509,22 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="217"/>
-      <c r="B34" s="217"/>
-      <c r="C34" s="217"/>
+      <c r="A34" s="211"/>
+      <c r="B34" s="211"/>
+      <c r="C34" s="211"/>
       <c r="D34" s="219"/>
     </row>
     <row r="35" spans="1:4" ht="35.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="205" t="s">
+      <c r="A35" s="212" t="s">
         <v>108</v>
       </c>
       <c r="B35" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="205" t="s">
+      <c r="C35" s="212" t="s">
         <v>116</v>
       </c>
-      <c r="D35" s="211">
+      <c r="D35" s="215">
         <v>10</v>
       </c>
     </row>
@@ -16391,65 +16534,65 @@
         <v>109</v>
       </c>
       <c r="C36" s="213"/>
-      <c r="D36" s="214"/>
+      <c r="D36" s="217"/>
     </row>
     <row r="37" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="206"/>
+      <c r="A37" s="214"/>
       <c r="B37" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="C37" s="206"/>
-      <c r="D37" s="212"/>
+      <c r="C37" s="214"/>
+      <c r="D37" s="216"/>
     </row>
     <row r="38" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="205" t="s">
+      <c r="A38" s="212" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="205" t="s">
+      <c r="B38" s="212" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="205" t="s">
+      <c r="C38" s="212" t="s">
         <v>134</v>
       </c>
-      <c r="D38" s="211">
+      <c r="D38" s="215">
         <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="206"/>
-      <c r="B39" s="206"/>
-      <c r="C39" s="206"/>
-      <c r="D39" s="212"/>
+      <c r="A39" s="214"/>
+      <c r="B39" s="214"/>
+      <c r="C39" s="214"/>
+      <c r="D39" s="216"/>
     </row>
     <row r="40" spans="1:4" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="205" t="s">
+      <c r="A40" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="B40" s="205" t="s">
+      <c r="B40" s="212" t="s">
         <v>135</v>
       </c>
-      <c r="C40" s="209"/>
-      <c r="D40" s="211">
+      <c r="C40" s="207"/>
+      <c r="D40" s="215">
         <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="206"/>
-      <c r="B41" s="206"/>
-      <c r="C41" s="210"/>
-      <c r="D41" s="212"/>
+      <c r="A41" s="214"/>
+      <c r="B41" s="214"/>
+      <c r="C41" s="209"/>
+      <c r="D41" s="216"/>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="205" t="s">
+      <c r="A42" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="205" t="s">
+      <c r="B42" s="212" t="s">
         <v>136</v>
       </c>
       <c r="C42" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="211">
+      <c r="D42" s="215">
         <v>30</v>
       </c>
     </row>
@@ -16459,7 +16602,7 @@
       <c r="C43" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="D43" s="214"/>
+      <c r="D43" s="217"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="213"/>
@@ -16467,7 +16610,7 @@
       <c r="C44" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D44" s="214"/>
+      <c r="D44" s="217"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="213"/>
@@ -16475,7 +16618,7 @@
       <c r="C45" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="D45" s="214"/>
+      <c r="D45" s="217"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="213"/>
@@ -16483,108 +16626,143 @@
       <c r="C46" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="214"/>
+      <c r="D46" s="217"/>
     </row>
     <row r="47" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="206"/>
-      <c r="B47" s="206"/>
+      <c r="A47" s="214"/>
+      <c r="B47" s="214"/>
       <c r="C47" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="212"/>
+      <c r="D47" s="216"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="209"/>
-      <c r="B48" s="205"/>
+      <c r="A48" s="207"/>
+      <c r="B48" s="212"/>
       <c r="C48" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="D48" s="211"/>
+      <c r="D48" s="215"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="215"/>
+      <c r="A49" s="208"/>
       <c r="B49" s="213"/>
       <c r="C49" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="D49" s="214"/>
+      <c r="D49" s="217"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="215"/>
+      <c r="A50" s="208"/>
       <c r="B50" s="213"/>
       <c r="C50" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="D50" s="214"/>
+      <c r="D50" s="217"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="215"/>
+      <c r="A51" s="208"/>
       <c r="B51" s="213"/>
       <c r="C51" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="D51" s="214"/>
+      <c r="D51" s="217"/>
     </row>
     <row r="52" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="210"/>
-      <c r="B52" s="206"/>
+      <c r="A52" s="209"/>
+      <c r="B52" s="214"/>
       <c r="C52" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="212"/>
+      <c r="D52" s="216"/>
     </row>
     <row r="53" spans="1:4" ht="89" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="205" t="s">
+      <c r="A53" s="212" t="s">
         <v>111</v>
       </c>
-      <c r="B53" s="207" t="s">
+      <c r="B53" s="220" t="s">
         <v>141</v>
       </c>
-      <c r="C53" s="209" t="s">
+      <c r="C53" s="207" t="s">
         <v>142</v>
       </c>
-      <c r="D53" s="211">
+      <c r="D53" s="215">
         <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="206"/>
-      <c r="B54" s="208"/>
-      <c r="C54" s="210"/>
-      <c r="D54" s="212"/>
+      <c r="A54" s="214"/>
+      <c r="B54" s="221"/>
+      <c r="C54" s="209"/>
+      <c r="D54" s="216"/>
     </row>
     <row r="55" spans="1:4" ht="128" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="205" t="s">
+      <c r="A55" s="212" t="s">
         <v>117</v>
       </c>
-      <c r="B55" s="205" t="s">
+      <c r="B55" s="212" t="s">
         <v>118</v>
       </c>
-      <c r="C55" s="205" t="s">
+      <c r="C55" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="211">
+      <c r="D55" s="215">
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="206"/>
-      <c r="B56" s="206"/>
-      <c r="C56" s="206"/>
-      <c r="D56" s="212"/>
+      <c r="A56" s="214"/>
+      <c r="B56" s="214"/>
+      <c r="C56" s="214"/>
+      <c r="D56" s="216"/>
     </row>
     <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="B42:B47"/>
+    <mergeCell ref="D42:D47"/>
+    <mergeCell ref="A48:A52"/>
+    <mergeCell ref="B48:B52"/>
+    <mergeCell ref="D48:D52"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="D27:D31"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="C13:C15"/>
@@ -16593,48 +16771,13 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="D27:D31"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="D42:D47"/>
-    <mergeCell ref="A48:A52"/>
-    <mergeCell ref="B48:B52"/>
-    <mergeCell ref="D48:D52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
